--- a/docs/LA-Q_SF-ICPMS_TAPP_v3.xlsx
+++ b/docs/LA-Q_SF-ICPMS_TAPP_v3.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithubC\USGIN\geochemBuildingBlocks\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F04169D-79DD-4CD0-8E38-AE8D902DB9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AA343C-5525-42D1-84DE-533E6CF993C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="2445" windowWidth="25065" windowHeight="14775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1215" windowWidth="26520" windowHeight="14805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAPP" sheetId="1" r:id="rId1"/>
     <sheet name="Legends" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TAPP!$A$1:$N$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TAPP!$A$1:$N$122</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2731" uniqueCount="1241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2737" uniqueCount="1247">
   <si>
     <t>Metadata Item</t>
   </si>
@@ -330,9 +330,6 @@
     <t>e.g., 'J. Smith (ORCID: 0000-0001-2345-6789)'</t>
   </si>
   <si>
-    <t>$Dataset.prov:wasGeneratedBy.schema:Agent/schema:Person.schema:name, schema:identifier</t>
-  </si>
-  <si>
     <t>N (Allan Patchen and Luca Fedele assisted with data collection per acknowledgments; not explicitly named as analysts in methods) [P20-Ack]</t>
   </si>
   <si>
@@ -458,12 +455,6 @@
     <t>e.g., http://doi.org/10.60520/IEDA/114187 | pending</t>
   </si>
   <si>
-    <t>$Dataset.schema:measuremntTechnique.schema:DefinedTerm.schema.name and schema.identifier</t>
-  </si>
-  <si>
-    <t>This should be the identifier for the protocol definition that the analysis level 'detail' is extenting for a particular dataset.</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
@@ -515,9 +506,6 @@
     <t>e.g., 'NASA 80NSSC21K0153; DFG WE 2850/5-1' | 'None'</t>
   </si>
   <si>
-    <t>$Dataset.schema:funding</t>
-  </si>
-  <si>
     <t>NASA Grants 80NSSC19K1238 (BZ), 80NSSC19K1613 (NLC), 80NSSC18K0595 (MH), NNX17AE77G (AER); NSF Cooperative Agreement DMR-1644779 and State of Florida [Acknowledgements]</t>
   </si>
   <si>
@@ -554,9 +542,6 @@
     <t>e.g., doi:10.1016/j.oregeorev.2011.11.001</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'techniquePublication'].</t>
-  </si>
-  <si>
     <t>target URL to publication , target name should be title of publication</t>
   </si>
   <si>
@@ -600,9 +585,6 @@
   </si>
   <si>
     <t>EPMA | SIMS | ICP-MS (solution) | Noble Gas MS | Other: specify | None</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:name</t>
   </si>
   <si>
     <t>range should be analytical technique vocabulary</t>
@@ -632,9 +614,6 @@
     <t>e.g., 'EPMA provides major element concentrations (SiO₂ as internal standard) used in LA-ICP-MS data reduction; EPMA performed first because LA-ICP-MS ablation is destructive' | 'SIMS isotope ratios cross-validated against LA-ICP-MS; SIMS performed first due to shallower beam penetration'</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:description</t>
-  </si>
-  <si>
     <t>text description of relationship</t>
   </si>
   <si>
@@ -666,9 +645,6 @@
     <t>2026-05-09</t>
   </si>
   <si>
-    <t>$Dataset.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:url</t>
-  </si>
-  <si>
     <t>Coupled Dataset or Publication Reference</t>
   </si>
   <si>
@@ -681,9 +657,6 @@
     <t>e.g., 'doi:10.26022/IEDA/112969' | same submission | pending | None</t>
   </si>
   <si>
-    <t>$Dataset.schema:relatedLink[].schema:linkRelationship[name =  'coupledDataset'].schema:target</t>
-  </si>
-  <si>
     <t>2. Samples</t>
   </si>
   <si>
@@ -694,12 +667,6 @@
   </si>
   <si>
     <t>Silicate glass | Feldspar | Pyroxene | Olivine | Oxide | Sulfide | Carbonate | Phosphate | Native metal | Iron meteorite | Fluid inclusion | Melt inclusion | Whole rock | Other: specify</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:object[].schema:DefinedTerm.schema.name</t>
-  </si>
-  <si>
-    <t>match. schema:object[] is an array of DefinedTerm or string describing target material (mineral phase, glass, oxide, etc.). Need vocabulary or target materials…</t>
   </si>
   <si>
     <t>read-only: True
@@ -836,9 +803,6 @@
     <t>e.g., 'Li-tetraborate, 1:2 (sample:flux)' | 'Li-metaborate/tetraborate 50:50, 1:5' | 'Not applicable (in situ)'</t>
   </si>
   <si>
-    <t xml:space="preserve">$MethodDefinition.schema:actionProcess.schema:step[][schema:name='samplePreparation'].schema:additionalProperty['Fusion Flux and Dilution Ratio'].schema:value </t>
-  </si>
-  <si>
     <t>two properties of sample preparation method</t>
   </si>
   <si>
@@ -920,9 +884,6 @@
     <t>e.g., '10 pre-ablation pulses discarded before acquisition (50 µm, 10 Hz, 2 J cm⁻²)' | '150 µm square spot, 2 J cm⁻², 20 Hz, 300 µm s⁻¹ pre-ablation pass (Chernonozhkin et al. 2021)' | 'None'</t>
   </si>
   <si>
-    <t xml:space="preserve">$MethodDefinition.schema:actionProcess.schema:step[][schema:name='samplePreparation'].schema:additionalProperty['Pre-Ablation Surface Treatment'].schema:value </t>
-  </si>
-  <si>
     <t xml:space="preserve"> property of sample preparation method</t>
   </si>
   <si>
@@ -953,12 +914,6 @@
     <t>e.g., 'ESI/NWR imageGEO193' | 'Coherent GeoLas HD' | 'Teledyne Analyte Excite 193' | 'Teledyne Analyte G2'</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:instrument[additionalType = 'Laser ablation system'].schema:manufacturer.schema:Organization.schema:name | .schema:instrument.schema:model.schema:name</t>
-  </si>
-  <si>
-    <t>match. CDIF instrument has manufacturer, and model. Have to parse the string in source data to identify manufacturer--typically the first token, from the model -- typically the rest of the string. Perhaps we can build up a lookup list of manufacturers--there aren't that many!</t>
-  </si>
-  <si>
     <t>ESI New Wave UP193FX (193 nm Nd:YAG frequency-quintupled solid state)</t>
   </si>
   <si>
@@ -998,12 +953,6 @@
     <t>e.g., 'Thermo Scientific iCAP TQ' | 'Agilent 7900' | 'Thermo Scientific Element XR' | 'TOFWERK icpTOF'</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:instrument.:additionalType[ICP-MS].schema:manufacturer.schema:Organization.schema:name | .schema:instrument.schema:model.schema:name</t>
-  </si>
-  <si>
-    <t>match. CDIF instrument has manufacturer, and model</t>
-  </si>
-  <si>
     <t>Thermo Fisher Scientific Element XR (SF-ICP-MS)</t>
   </si>
   <si>
@@ -1026,9 +975,6 @@
   </si>
   <si>
     <t>Single-collector quadrupole (Q-ICP-MS) | Single-collector sector-field (SF-ICP-MS) | Multi-collector sector-field (MC-ICP-MS) | Time-of-flight (ICP-ToF-MS) | Triple quadrupole (ICP-MS/MS) | Other: specify</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:instrument.schema:additionalType[ICP-MS].schema:name</t>
   </si>
   <si>
     <t>dataType: string;  
@@ -1087,9 +1033,6 @@
     <t>e.g., 'Ni standard sample cone + Ni H-type skimmer' | 'Al standard sample cone + Al H-type skimmer (1.1 mm aperture)' | 'Pt sample cone + Pt skimmer'</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:instrument.:additionalType[ICP-MS]schema:hasPart[].additionalType [ 'Interface Cone']. Schema:name</t>
-  </si>
-  <si>
     <t>property:interfaceConeConfiguration 
 dataType: string 
 readOnly: True</t>
@@ -1119,9 +1062,6 @@
     <t>Nickel (Ni) sampler and skimmer cones (standard configuration); Platinum (Pt) sampler, nickel (Ni) skimmer</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:instrument.:additionalType[ICP-MS]schema:hasPart[].additionalType [ 'Interface Cone']. schema:additiionalProperty['Sampler and Skimmer Cone Material'].schema:value</t>
-  </si>
-  <si>
     <t>parameter:samplerAndSkimmerConeMaterial dataType: string readOnly: True</t>
   </si>
   <si>
@@ -1132,9 +1072,6 @@
   </si>
   <si>
     <t>5 mm; Standard position (manufacturer default; not explicitly reported)</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:instrument.:additionalType[ICP-MS]schema:additionalProperty['Torch Depth']. Schema:value</t>
   </si>
   <si>
     <t>parameter:torchDepth
@@ -1158,9 +1095,6 @@
   </si>
   <si>
     <t>On | Off | Not applicable (instrument does not have guard electrode)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$MethodDefinition.schema:actionProcess.schema:step[][schema:name='dataAquisition'].schema:additionalProperty['Guard Electrode'].schema:value </t>
   </si>
   <si>
     <t>property:guardElectrode 
@@ -1184,9 +1118,6 @@
     <t>SF-ICP-MS: adjustable mass resolution (300–10,000); Q-ICP-MS: unit resolution only</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:instrument.:additionalType[ICP-MS]schema:additionalProperty['Mass Resolution Setting']. Schema:value</t>
-  </si>
-  <si>
     <t>property:massResolutionSetting
 dataType: string 
 readOnly: False</t>
@@ -1225,9 +1156,6 @@
     <t>e.g., 'Single SEM, dual mode (pulse counting and analog)' | 'Single SEM in triple mode (pulse, analog, Faraday)' | 'Nine Faraday cups + one ion counter (MC)'</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:instrument.schema:additionalProperty['Detector Configuration']. Schema:value</t>
-  </si>
-  <si>
     <t>dataType: string; 
 readOnly: True</t>
   </si>
@@ -1269,9 +1197,6 @@
   </si>
   <si>
     <t>e.g., '193 nm ArF excimer' | '213 nm Nd:YAG frequency-quintupled' | '257 nm Yb:KGW femtosecond' | '1030 nm Yb:KGW IR femtosecond'</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:instrument.additionalType['Laser'].additionalProperty[ 'Laser Wavelength and Type'].schema:value</t>
   </si>
   <si>
     <t>dataType: string 
@@ -1373,9 +1298,6 @@
   </si>
   <si>
     <t>e.g., 'Two-volume HelEx II (Müller et al. 2009)' | 'HDIP low-dispersion tube-type cell' | 'Single-volume standard cell' | 'ARIS (Aerosol Rapid Introduction System)'</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:instrument.:additionalType[ICP-MS].schema:hasPart[].additionalType[ 'Ablation Cell']. Schema:name</t>
   </si>
   <si>
     <t>HELEX II two-volume ablation cell</t>
@@ -1432,9 +1354,6 @@
     <t>e.g., '25 µm circular' | '20×20 µm square' | '15 or 25 µm circular (phase-dependent)'</t>
   </si>
   <si>
-    <t>$MethodDefinition.ada:spotGeometry</t>
-  </si>
-  <si>
     <t>property:spotGeometry
   dataType: string
   readOnly: False</t>
@@ -1486,12 +1405,6 @@
   </si>
   <si>
     <t>Spot (stationary) | Transect (continuous line scan) | Raster area (2D elemental mapping) | Stepped line profile | Other: specify</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.ada:spotPath, ada:ablationMode</t>
-  </si>
-  <si>
-    <t>two properties</t>
   </si>
   <si>
     <t>property:spotPath
@@ -1538,9 +1451,6 @@
     <t>e.g., 0.001 mJ | 3.5 mJ</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:additionalProperty['Laser Energy']. schema.defaultValue</t>
-  </si>
-  <si>
     <t>parameter:laserEnergy
   dataType: propertyValueSpecification
   readOnly: False</t>
@@ -1564,9 +1474,6 @@
     <t>2026-05-07</t>
   </si>
   <si>
-    <t>$MethodDefinition.ada:laserFluence</t>
-  </si>
-  <si>
     <t xml:space="preserve">property: laserFluence
   readOnly: False
   dataType: string </t>
@@ -1617,9 +1524,6 @@
     <t>2026-05-13</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:additionalProperty['Laser Beam Energy Profile'].schema:value</t>
-  </si>
-  <si>
     <t>dataType: PropertyValue
 readOnly: True</t>
   </si>
@@ -1634,9 +1538,6 @@
   </si>
   <si>
     <t>e.g., 5 | 10 | 20 | 100</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.ada:laserRepetitionRate</t>
   </si>
   <si>
     <t>property:  laserRepetitionRate. 
@@ -1674,9 +1575,6 @@
     <t>e.g., '4 ns (ArF excimer)' | '20 ns' | '290 fs (Yb:KGW)' | '220 fs (Ti:sapphire)'</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:additionalProperty['Laser Pulse Duration'].schema:value</t>
-  </si>
-  <si>
     <t>N (UP193FX; ns solid-state; pulse duration not reported)</t>
   </si>
   <si>
@@ -1755,9 +1653,6 @@
   </si>
   <si>
     <t>e.g., '5 µm s⁻¹ (transect)' | '9 µm s⁻¹ (raster mapping, 20×20 µm spot, 20 Hz)' | '20 µm step size' | '0.3–30 mm² h⁻¹ (mapping rate range)'</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:additionalProperty['Transect Rate, Mapping Rate or Step Size'].schema:defaultValue</t>
   </si>
   <si>
     <t xml:space="preserve">  parameter:transectOrMappingRateOrStepSize
@@ -1864,9 +1759,6 @@
     <t>e.g., 'Ar make-up gas, 0.95 l min⁻¹' | 'Ar make-up 0.80 l min⁻¹ + N₂ 2 ml min⁻¹ (sensitivity enhancement)' | 'None (no N₂ added)'</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:additionalProperty['Plasma, Make-up Gas Addition'].schema:defaultValue</t>
-  </si>
-  <si>
     <t xml:space="preserve">  dataType:  schema:propertyValueSpecification
   readOnly: False
 </t>
@@ -2019,9 +1911,6 @@
     <t>e.g., 'Squid 2.0 (laurin technik)' | 'ARIS (Aerosol Rapid Introduction System)' | 'None'</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:additionalProperty['Signal Smoothing'].schema:defaultValue</t>
-  </si>
-  <si>
     <t xml:space="preserve">parameter: signalSmoothing
   dataType:  schema:propertyValueSpecification
   readOnly: False
@@ -2046,9 +1935,6 @@
     <t>e.g., 'Daily auto-tune on NIST SRM 612; optimised for max sensitivity on ¹³⁹La and ²³²Th with ThO⁺/Th⁺ &lt;0.5% and U/Th = 1.0 ± 0.05'</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:additionalProperty['ICP Tuning'].schema:defaultValue</t>
-  </si>
-  <si>
     <t xml:space="preserve">parameter: icPlasmaTuning
   dataType:  schema:propertyValueSpecification
   readOnly: False
@@ -2123,9 +2009,6 @@
     <t>e.g., 'ThO⁺/Th⁺ = 0.3% (threshold &lt;0.5% met)' | 'ThO⁺/Th⁺ = 0.08%' | 'CeO⁺/Ce⁺ = 0.7% (threshold &lt;1.0% met)'</t>
   </si>
   <si>
-    <t>$Dataset.dqv:hasQualityMeasurement.dqv:isMeasurementOf='Measured oxide production ratio'.dqv:value</t>
-  </si>
-  <si>
     <t>parameter:oxideProduction 
 dataType: string 
 readOnly: False</t>
@@ -2143,9 +2026,6 @@
     <t>¹³⁸Ba²⁺/¹³⁸Ba⁺ (m/z 69/138); Ce²⁺/Ce⁺ (m/z 70/140); ²³⁸U²⁺/²³⁸U⁺ (m/z 119/238)</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:additionalProperty['Doubly-Charged Species Monitor'].schema:defaultValue</t>
-  </si>
-  <si>
     <t>parameter:doublyChargedSpeciesMonitor dataType: PropertyValueSpecification 
 readOnly: False</t>
   </si>
@@ -2157,9 +2037,6 @@
   </si>
   <si>
     <t>&lt;1% (threshold); 0.4% (measured, ¹³⁸Ba²⁺/¹³⁸Ba⁺); N (not reported)</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:additionalProperty['Doubly-Charged Species Production'].schema:defaultValue</t>
   </si>
   <si>
     <t>parameter:doublyChargedSpeciesProduction dataType: PropertyValueSpecification 
@@ -2518,10 +2395,6 @@
     <t>e.g., 'X = 12350 µm, Y = 8760 µm (stage coordinates)' | '500 µm from metal-olivine rim toward core' | 'Map centre: X=15000, Y=9000 µm; area: 1450×600 µm'</t>
   </si>
   <si>
-    <t xml:space="preserve">$Dataset.schema.object[$type = schema:Thing].schema.name = 'mapped area description'.schema.description
-</t>
-  </si>
-  <si>
     <t>if is X, Y  coordinates of spot, is analysis Level; if is  coordinates locating a mapped area, is DataSet level text. 
 Spot spatial reference defines the origin, axis orientation, and scael for the spot coordinates.</t>
   </si>
@@ -2540,9 +2413,6 @@
   </si>
   <si>
     <t>e.g., 3 (three replicate spots per grain) | 1 (single transect) | 1 (single map)</t>
-  </si>
-  <si>
-    <t>$Dataset.prov:wasGeneratedBy.schema:additionalProperty [name = 'Number Of Replicates'].schema:value</t>
   </si>
   <si>
     <t>parameter:numberOfReplicates 
@@ -2830,9 +2700,6 @@
   </si>
   <si>
     <t>e.g., Counting statistics only (1σ on integrated signal, Longerich et al. 1996) | SD of n replicate analyses used as combined uncertainty estimate | Full propagation: counting + calibration standard + IS uncertainty (specify formula)</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:Uncertainty Propagation Method'].schema:defaultValue</t>
   </si>
   <si>
     <t xml:space="preserve">parameter: uncertaintyPropagationMethod
@@ -3344,9 +3211,6 @@
     <t>e.g., 'None' | '100% oxide sum normalization applied per pixel to enforce mass balance (Liu et al. 2008)' | 'Normalized to ⁸⁸Sr/⁸⁶Sr = 8.37521 for mass bias correction in Sr isotope analysis'</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:additionalProperty['Normalization / Standards-Based Correction'].schema:defaultValue</t>
-  </si>
-  <si>
     <t xml:space="preserve">parameter: postAcquisitionNormalization
   dataType:  schema:propertyValueSpecification
   readOnly: False
@@ -3402,9 +3266,6 @@
   </si>
   <si>
     <t>e.g., 'NIST SRM 612 (Jochum et al. 2011, doi:10.1111/j.1751-908X.2011.00120.x)' | 'USGS BCR-2G (GeoReM preferred values, georem.mpch-mainz.gwdg.de)'</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.ada:primaryCalibrationStandardName</t>
   </si>
   <si>
     <t>array</t>
@@ -3780,9 +3641,6 @@
     <t>Any additional context about this protocol or analysis session not captured by the structured fields above. Use sparingly; structured fields are preferred for all information that can be formally categorised.</t>
   </si>
   <si>
-    <t>$.schema:description</t>
-  </si>
-  <si>
     <t>method Property: schema:description accepts free-text narrative; additional notes can extend it or be distributed to the most relevant workflow step's schema:description.</t>
   </si>
   <si>
@@ -3863,13 +3721,7 @@
     <t>This field does not apply to this analytical mode.</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:location.schema:Place.schema:name</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:instrument.schema:additionalProperty['Collision-ReactionCellConfiguration']. Schema:value</t>
   </si>
   <si>
     <t>property:carrierGasFlowRate 
@@ -3898,9 +3750,6 @@
 readOnly: False</t>
   </si>
   <si>
-    <t>$MethodDefinition.ada:signalCollectionMethod</t>
-  </si>
-  <si>
     <t>property:massResolutionPerAnalyte
 dataType: string 
 readOnly: True</t>
@@ -3924,15 +3773,9 @@
 readOnly: False</t>
   </si>
   <si>
-    <t>$MethodDefinition.ada:cellExitDiscriminationVoltage</t>
-  </si>
-  <si>
     <t>property:cellExitDiscriminationVoltage
 dataType: decimal 
 readOnly: False</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.ada:gasFlowRate</t>
   </si>
   <si>
     <t>property:gasFlowRate
@@ -4049,9 +3892,6 @@
     </r>
   </si>
   <si>
-    <t>$MethodDefinition.ada:collisionGasType</t>
-  </si>
-  <si>
     <t>property:collisionGasType
 dataType: string 
 readOnly: True</t>
@@ -4091,9 +3931,6 @@
   readOnly: True</t>
   </si>
   <si>
-    <t>$MethodDefinition.ada:calibrationStandardMeasurementFrequency</t>
-  </si>
-  <si>
     <t>property: calibrationStandardMeasurementFrequency ;
   datatype: string ;
   readOnly: True</t>
@@ -4138,6 +3975,187 @@
   </si>
   <si>
     <t>$MethodDefinition.ada:elementalFractionationCorrection[]</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:additionalProperty[schema:name='Detector Configuration'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:additionalProperty[schema:name='Mass Resolution Setting'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:hasPart[schema:additionalType='Torch'].schema:name</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:hasPart[schema:additionalType='Torch'].schema:additionalProperty[schema:name='Torch Depth'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.ada:ablationSamplingMode</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='Laser ablation system'].ada:laserRepetitionRate</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='Laser ablation system'].ada:laserFlueence</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='Laser ablation system'].ada:laserSpotGeometry</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='Laser ablation system'].ada:laserType</t>
+  </si>
+  <si>
+    <t>match. CDIF instrument has manufacturer, and model. Parsing this free text string to distinguish manufacturer and model is unreliable; decide it should all go in instrument/model/name field.</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='Laser ablation system'].schema:name</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:description</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.ada:primaryStandardName</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.ada:calibrationMeasurementFrequency</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:additionalProperty['Normalization or Correction'].schema:defaultValue</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:additionalType</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:identifier</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:model.schema:name</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:location.schema:Place.schema:defaultname</t>
+  </si>
+  <si>
+    <t>match. schema:object[] has a Target Material property; the value can be a DefinedTerm or string describing target material (mineral phase, glass, oxide, etc.). Need vocabulary for target materials…</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:additionalProperty[schema:name='Triple Scanning Mode'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:additionalProperty[schema:name='e-scanRange'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:object[@type ="schema:Thing",  "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:additionalProperty[schema:name = 'Sample Form'].schema.defaultvalue</t>
+  </si>
+  <si>
+    <t>parse name and identifier if possible</t>
+  </si>
+  <si>
+    <t>This should be the identifier for the most specific protocol description; different from the @id for the TAPP definition JSON-LD object.  Should be a DOI</t>
+  </si>
+  <si>
+    <t>$cdifDiscovery.schema:measurementTechnique.schema:DefinedTerm.schema.identifier</t>
+  </si>
+  <si>
+    <t>$cdifCore.schema:funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$Dataset.prov:wasGeneratedBy.schema:object[@type = "schema:Thing",  "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema.additionalProperty[schema:name = 'mapped area description'].schema.value
+</t>
+  </si>
+  <si>
+    <t>$cdifDiscovery.dqv:hasQualityMeasurement.dqv:isMeasurementOf='Oxide production ratio'.dqv:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:additionalProperty[schema:name='Uncertainty Propagation Method'].schema:defaultValue</t>
+  </si>
+  <si>
+    <t>$cdifCore.schema:contributor[schema:roleName='analyst'].schema.name</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:object[@type ="schema:Thing",  "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:additionalProperty[schema:name = 'Target Material'].schema.value[]</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.ada:signalCollectionMode</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:hasPart[schema:additionalType='Collision Reaction Cell'].schema:name</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType = 'Laser ablation system'].schema:model.schema:name</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:hasPart[schema:additionalType= 'Collision Reaction Cell'].schema:additionalProperty[schema:name='Collision Gas'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:hasPart[schema:additionalType = 'Collision Reaction Cell'].schema:additionalProperty[schema:name='Cell Exit Voltage'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:hasPart[schema:additionalType='Collision Reaction Cell'].schema:additionalProperty[schema:name='Reaction Gas'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:hasPart[schema:additionalType='Collision Reaction Cell'].schema:additionalProperty[schema:name='Reaction Gas Flow Rate'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:hasPart[schema:additionalType='Interface Cone'].schema:additionalProperty[schema:name='Configuration'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:hasPart[schema:additionalType='Interface Cone'].schema:additionalProperty[schema:name='Sampler and Skimmer Cone Material'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='Laser ablation system'].schema:additionalProperty[schema:name='Laser Beam Energy Profile'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='ICP-MS'].schema:hasPart[schema:additionalType='Collision Reaction Cell'].schema:additionalProperty[schema:name='Gas Flow Rate'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='Laser ablation system'].schema:additionalProperty[schema:name='Laser Energy']. schema.defaultValue</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument[schema:additionalType='Laser ablation system'].schema:additionalProperty[schema:name='Laser Pulse Duration'].schema:value</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[schema:name =  'techniquePublication'].schema:target.schema:name</t>
+  </si>
+  <si>
+    <t>$Dataset.schema:relatedLink[].schema:linkRelationship[schema:name =  'coupledTechnique'].schema:target.schema:name</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[schema:name =  'coupledTechnique'].schema:target.schema:description</t>
+  </si>
+  <si>
+    <t>$cdifCore.schema:relatedLink[].schema:linkRelationship[schema:name =  'coupledProtocol'].schema:target.schema:url</t>
+  </si>
+  <si>
+    <t>$Dataset.prov:wasGeneratedBy.schema:additionalProperty [schema:name = 'Number Of Replicates'].schema:value</t>
+  </si>
+  <si>
+    <t>$cdifCore.schema:relatedLink[].schema:linkRelationship[schema:name =  'coupledDataset'].schema:target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$MethodDefinition.schema:actionProcess.schema:step[][schema:name='samplePreparation'].schema:additionalProperty[schema:name = 'Fusion Flux and Dilution Ratio'].schema:value </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$MethodDefinition.schema:actionProcess.schema:step[][schema:name='samplePreparation'].schema:additionalProperty[schema:name = 'Pre-Ablation Surface Treatment'].schema:value </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$MethodDefinition.schema:actionProcess.schema:step[][schema:name='dataAquisition'].schema:additionalProperty[schema:name = 'Guard Electrode'].schema:value </t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:additionalProperty[schema:name = 'Transect Rate, Mapping Rate or Step Size'].schema:defaultValue</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:additionalProperty[schema:name = 'Plasma, Make-up Gas Addition'].schema:defaultValue</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:additionalProperty[schema:name = 'Signal Smoothing'].schema:defaultValue</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:additionalProperty[schema:name = 'ICP Tuning'].schema:defaultValue</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:additionalProperty[schema:name = 'Doubly-Charged Species Monitor'].schema:defaultValue</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:additionalProperty[schema:name = 'Doubly-Charged Species Production'].schema:defaultValue</t>
   </si>
 </sst>
 </file>
@@ -4624,7 +4642,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB123"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AB122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -4636,9 +4655,9 @@
     <col min="7" max="7" width="20.5703125" customWidth="1"/>
     <col min="8" max="8" width="13.5703125" customWidth="1"/>
     <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" customWidth="1"/>
-    <col min="12" max="12" width="32.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="12" max="12" width="36.140625" style="1" customWidth="1"/>
     <col min="13" max="13" width="30" style="1" customWidth="1"/>
     <col min="14" max="14" width="45" style="1" customWidth="1"/>
     <col min="15" max="15" width="30" customWidth="1"/>
@@ -4734,7 +4753,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
@@ -4767,7 +4786,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
@@ -4844,7 +4863,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>50</v>
       </c>
@@ -4921,7 +4940,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
@@ -5001,7 +5020,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>73</v>
       </c>
@@ -5032,7 +5051,10 @@
         <v>36</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>77</v>
+        <v>1217</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>1210</v>
       </c>
       <c r="O6" s="9"/>
       <c r="P6" s="1" t="s">
@@ -5069,30 +5091,30 @@
         <v>29</v>
       </c>
       <c r="AA6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AB6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" spans="1:28" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -5106,70 +5128,70 @@
         <v>36</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="R7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T7" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="R7" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="T7" s="1" t="s">
+      <c r="U7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="V7" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="W7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X7" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="W7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X7" s="1" t="s">
+      <c r="Y7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="1" t="s">
+      <c r="Z7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA7" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="Z7" s="1" t="s">
+      <c r="AB7" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AA7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AB7" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -5183,13 +5205,13 @@
         <v>36</v>
       </c>
       <c r="L8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="O8" s="9"/>
       <c r="P8" s="1" t="s">
@@ -5232,12 +5254,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>32</v>
@@ -5246,10 +5268,10 @@
         <v>33</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -5263,13 +5285,13 @@
         <v>36</v>
       </c>
       <c r="L9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="O9" s="9"/>
       <c r="P9" s="1" t="s">
@@ -5312,12 +5334,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>75</v>
@@ -5326,10 +5348,10 @@
         <v>32</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -5343,10 +5365,10 @@
         <v>36</v>
       </c>
       <c r="L10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="1" t="s">
@@ -5389,12 +5411,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>75</v>
@@ -5403,10 +5425,10 @@
         <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -5420,7 +5442,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O11" s="9"/>
       <c r="P11" s="1" t="s">
@@ -5463,12 +5485,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>75</v>
@@ -5477,10 +5499,10 @@
         <v>32</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -5494,13 +5516,13 @@
         <v>36</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>119</v>
+        <v>1212</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>120</v>
+        <v>1211</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O12" s="9"/>
       <c r="P12" s="1" t="s">
@@ -5543,12 +5565,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>32</v>
@@ -5560,11 +5582,11 @@
         <v>34</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>36</v>
@@ -5576,10 +5598,10 @@
         <v>36</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>38</v>
@@ -5589,48 +5611,48 @@
         <v>29</v>
       </c>
       <c r="Q13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="V13" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="W13" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="S13" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U13" s="1" t="s">
+      <c r="X13" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="V13" s="1" t="s">
+      <c r="Y13" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="W13" s="1" t="s">
+      <c r="Z13" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="X13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z13" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB13" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" ht="105" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>75</v>
@@ -5642,11 +5664,11 @@
         <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>36</v>
@@ -5658,67 +5680,67 @@
         <v>36</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>138</v>
+        <v>1213</v>
       </c>
       <c r="O14" s="9"/>
       <c r="P14" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="W14" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="Q14" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="T14" s="1" t="s">
+      <c r="X14" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="U14" s="1" t="s">
+      <c r="Y14" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="V14" s="1" t="s">
+      <c r="Z14" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA14" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="W14" s="1" t="s">
+      <c r="AB14" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="X14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="Y14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="Z14" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA14" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AB14" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C15" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -5732,77 +5754,77 @@
         <v>36</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>151</v>
+        <v>1232</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>38</v>
       </c>
       <c r="O15" s="9"/>
       <c r="P15" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="X15" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="Q15" s="1" t="s">
+      <c r="Y15" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="R15" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="T15" s="1" t="s">
+      <c r="Z15" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="U15" s="1" t="s">
+      <c r="AA15" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="V15" s="1" t="s">
+      <c r="AB15" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="W15" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="X15" s="1" t="s">
+    </row>
+    <row r="16" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Y15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="Z15" s="1" t="s">
+      <c r="C16" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="AA15" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="AB15" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>36</v>
@@ -5814,17 +5836,17 @@
         <v>36</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>167</v>
+        <v>1233</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="O16" s="9"/>
       <c r="P16" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="Q16" s="1" t="s">
         <v>29</v>
@@ -5839,7 +5861,7 @@
         <v>29</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="V16" s="1" t="s">
         <v>29</v>
@@ -5857,34 +5879,34 @@
         <v>29</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>36</v>
@@ -5896,17 +5918,17 @@
         <v>36</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>176</v>
+        <v>1234</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="O17" s="9"/>
       <c r="P17" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>29</v>
@@ -5921,7 +5943,7 @@
         <v>29</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="V17" s="1" t="s">
         <v>29</v>
@@ -5939,34 +5961,34 @@
         <v>29</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>75</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>36</v>
@@ -5978,7 +6000,7 @@
         <v>36</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>187</v>
+        <v>1235</v>
       </c>
       <c r="O18" s="9"/>
       <c r="P18" s="1" t="s">
@@ -6021,28 +6043,28 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>75</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>36</v>
@@ -6054,7 +6076,7 @@
         <v>36</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>192</v>
+        <v>1237</v>
       </c>
       <c r="O19" s="9"/>
       <c r="P19" s="1" t="s">
@@ -6097,10 +6119,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="8.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -6131,12 +6153,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>32</v>
@@ -6145,10 +6167,10 @@
         <v>33</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -6162,73 +6184,73 @@
         <v>36</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>197</v>
+        <v>1218</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>198</v>
+        <v>1206</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="O22" s="9"/>
       <c r="P22" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="Q22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="V22" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="X22" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y22" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z22" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="AA22" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB22" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" ht="120" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -6242,61 +6264,61 @@
         <v>36</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>197</v>
+        <v>1209</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="O23" s="9"/>
       <c r="P23" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA23" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="Q23" s="1" t="s">
+      <c r="AB23" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="R23" s="1" t="s">
+    </row>
+    <row r="24" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="S23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="X23" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="Y23" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA23" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB23" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" ht="90" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>75</v>
@@ -6308,7 +6330,7 @@
         <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -6322,7 +6344,7 @@
         <v>36</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="O24" s="9"/>
       <c r="P24" s="1" t="s">
@@ -6359,30 +6381,30 @@
         <v>29</v>
       </c>
       <c r="AA24" s="1" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -6396,7 +6418,7 @@
         <v>36</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="O25" s="9"/>
       <c r="P25" s="1" t="s">
@@ -6439,24 +6461,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -6470,13 +6492,13 @@
         <v>36</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>242</v>
+        <v>1238</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O26" s="9"/>
       <c r="P26" s="1" t="s">
@@ -6504,7 +6526,7 @@
         <v>75</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="Y26" s="1" t="s">
         <v>75</v>
@@ -6513,30 +6535,30 @@
         <v>75</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="180" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -6550,73 +6572,73 @@
         <v>36</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="O27" s="9"/>
       <c r="P27" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA27" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB27" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="Q27" s="1" t="s">
+    </row>
+    <row r="28" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="R27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="S27" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="V27" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="W27" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="X27" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="Y27" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="Z27" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="AA27" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="AB27" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28" ht="90" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C28" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -6630,29 +6652,29 @@
         <v>36</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>269</v>
+        <v>1239</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O28" s="9"/>
       <c r="P28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="U28" s="1" t="s">
         <v>29</v>
@@ -6664,7 +6686,7 @@
         <v>29</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="Y28" s="1" t="s">
         <v>29</v>
@@ -6673,16 +6695,16 @@
         <v>29</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" ht="8.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -6713,12 +6735,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>32</v>
@@ -6730,11 +6752,11 @@
         <v>34</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>36</v>
@@ -6746,61 +6768,61 @@
         <v>36</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>280</v>
+        <v>1221</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>281</v>
+        <v>1196</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>38</v>
       </c>
       <c r="O31" s="9"/>
       <c r="P31" s="1" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="AA31" s="1" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>32</v>
@@ -6812,7 +6834,7 @@
         <v>34</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -6826,61 +6848,61 @@
         <v>36</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>295</v>
+        <v>1204</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>296</v>
+        <v>1196</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>38</v>
       </c>
       <c r="O32" s="9"/>
       <c r="P32" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="AA32" s="1" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>32</v>
@@ -6892,11 +6914,11 @@
         <v>52</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>36</v>
@@ -6908,77 +6930,77 @@
         <v>36</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>305</v>
+        <v>1202</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>1205</v>
+        <v>1157</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="O33" s="9"/>
       <c r="P33" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="AA33" s="1" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="AB33" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>36</v>
@@ -6989,7 +7011,9 @@
       <c r="K34" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L34" s="21"/>
+      <c r="L34" s="1" t="s">
+        <v>1203</v>
+      </c>
       <c r="O34" s="9"/>
       <c r="P34" s="1" t="s">
         <v>29</v>
@@ -7031,12 +7055,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>32</v>
@@ -7048,11 +7072,11 @@
         <v>34</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>36</v>
@@ -7064,38 +7088,38 @@
         <v>36</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>324</v>
+        <v>1226</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>1205</v>
+        <v>1157</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="O35" s="9"/>
       <c r="P35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="X35" s="1" t="s">
         <v>29</v>
@@ -7113,28 +7137,28 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>36</v>
@@ -7146,10 +7170,10 @@
         <v>36</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>334</v>
+        <v>1227</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="O36" s="9"/>
       <c r="P36" s="1"/>
@@ -7166,28 +7190,28 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
     </row>
-    <row r="37" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>36</v>
@@ -7199,10 +7223,10 @@
         <v>36</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>339</v>
+        <v>1190</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="O37" s="9"/>
       <c r="P37" s="1"/>
@@ -7219,15 +7243,15 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
     </row>
-    <row r="38" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>33</v>
@@ -7236,11 +7260,11 @@
         <v>34</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>36</v>
@@ -7251,7 +7275,9 @@
       <c r="K38" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L38" s="21"/>
+      <c r="L38" s="1" t="s">
+        <v>1189</v>
+      </c>
       <c r="O38" s="9"/>
       <c r="P38" s="1" t="s">
         <v>29</v>
@@ -7293,12 +7319,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>32</v>
@@ -7310,7 +7336,7 @@
         <v>52</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -7324,10 +7350,10 @@
         <v>36</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>347</v>
+        <v>1240</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="O39" s="9"/>
       <c r="P39" s="1" t="s">
@@ -7349,10 +7375,10 @@
         <v>29</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="X39" s="1" t="s">
         <v>29</v>
@@ -7370,30 +7396,30 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>36</v>
@@ -7405,58 +7431,58 @@
         <v>36</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>354</v>
+        <v>1188</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="O40" s="9"/>
       <c r="P40" s="1" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="AA40" s="1" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>32</v>
@@ -7468,7 +7494,7 @@
         <v>34</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -7482,38 +7508,38 @@
         <v>36</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>367</v>
+        <v>1187</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="O41" s="9"/>
       <c r="P41" s="1" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U41" s="1" t="s">
         <v>29</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="Y41" s="1" t="s">
         <v>29</v>
@@ -7528,12 +7554,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="345" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>32</v>
@@ -7545,13 +7571,13 @@
         <v>52</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>36</v>
@@ -7563,10 +7589,10 @@
         <v>36</v>
       </c>
       <c r="L42" s="21" t="s">
-        <v>1206</v>
+        <v>1220</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="O42" s="9"/>
       <c r="P42" s="1" t="s">
@@ -7609,12 +7635,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>32</v>
@@ -7626,11 +7652,11 @@
         <v>34</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>36</v>
@@ -7642,70 +7668,70 @@
         <v>36</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>382</v>
+        <v>1195</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="O43" s="9"/>
       <c r="P43" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="X43" s="1" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="Z43" s="1" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="AA43" s="1" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -7719,13 +7745,13 @@
         <v>36</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="O44" s="9"/>
       <c r="P44" s="1" t="s">
@@ -7768,28 +7794,28 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>36</v>
@@ -7801,41 +7827,41 @@
         <v>36</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="O45" s="9"/>
       <c r="P45" s="1" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="X45" s="1" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="Y45" s="1" t="s">
         <v>29</v>
@@ -7844,21 +7870,21 @@
         <v>29</v>
       </c>
       <c r="AA45" s="1" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>33</v>
@@ -7867,11 +7893,11 @@
         <v>34</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I46" s="8" t="s">
         <v>36</v>
@@ -7883,44 +7909,44 @@
         <v>36</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>415</v>
+        <v>1197</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="O46" s="9"/>
       <c r="P46" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="U46" s="1" t="s">
         <v>29</v>
       </c>
       <c r="V46" s="1" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="X46" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Y46" s="1" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="Z46" s="1" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="AA46" s="1" t="s">
         <v>29</v>
@@ -7929,10 +7955,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="8.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:28" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -7963,12 +7989,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>32</v>
@@ -7977,14 +8003,14 @@
         <v>33</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>36</v>
@@ -7996,13 +8022,13 @@
         <v>36</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>14</v>
@@ -8021,28 +8047,28 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
     </row>
-    <row r="50" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>36</v>
@@ -8054,58 +8080,58 @@
         <v>36</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>433</v>
+        <v>1194</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="O50" s="9"/>
       <c r="P50" s="1" t="s">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>438</v>
+        <v>411</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="U50" s="1" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="V50" s="1" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="Y50" s="1" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="Z50" s="1" t="s">
-        <v>445</v>
+        <v>418</v>
       </c>
       <c r="AA50" s="1" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="AB50" s="1" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
     </row>
     <row r="51" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>32</v>
@@ -8117,11 +8143,11 @@
         <v>52</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>36</v>
@@ -8133,73 +8159,70 @@
         <v>36</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>452</v>
+        <v>1191</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>453</v>
+        <v>424</v>
       </c>
       <c r="O51" s="9"/>
       <c r="P51" s="1" t="s">
-        <v>454</v>
+        <v>425</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>455</v>
+        <v>426</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>456</v>
+        <v>427</v>
       </c>
       <c r="S51" s="1" t="s">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="U51" s="1" t="s">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="V51" s="1" t="s">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>455</v>
+        <v>426</v>
       </c>
       <c r="X51" s="1" t="s">
-        <v>458</v>
+        <v>429</v>
       </c>
       <c r="Y51" s="1" t="s">
-        <v>459</v>
+        <v>430</v>
       </c>
       <c r="Z51" s="1" t="s">
-        <v>460</v>
+        <v>431</v>
       </c>
       <c r="AA51" s="1" t="s">
-        <v>461</v>
+        <v>432</v>
       </c>
       <c r="AB51" s="1" t="s">
-        <v>461</v>
+        <v>432</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>462</v>
+        <v>433</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>464</v>
+        <v>435</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -8213,10 +8236,10 @@
         <v>36</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>466</v>
+        <v>1230</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="O52" s="9"/>
       <c r="P52" s="1" t="s">
@@ -8253,34 +8276,34 @@
         <v>29</v>
       </c>
       <c r="AA52" s="1" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="AB52" s="1" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
     </row>
-    <row r="53" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>36</v>
@@ -8292,74 +8315,74 @@
         <v>36</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>474</v>
+        <v>1193</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="O53" s="9"/>
       <c r="P53" s="1" t="s">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>477</v>
+        <v>446</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>478</v>
+        <v>447</v>
       </c>
       <c r="S53" s="1" t="s">
-        <v>479</v>
+        <v>448</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U53" s="1" t="s">
-        <v>480</v>
+        <v>449</v>
       </c>
       <c r="V53" s="1" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="X53" s="1" t="s">
-        <v>482</v>
+        <v>451</v>
       </c>
       <c r="Y53" s="1" t="s">
-        <v>483</v>
+        <v>452</v>
       </c>
       <c r="Z53" s="1" t="s">
-        <v>484</v>
+        <v>453</v>
       </c>
       <c r="AA53" s="1" t="s">
-        <v>485</v>
+        <v>454</v>
       </c>
       <c r="AB53" s="1" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>36</v>
@@ -8371,10 +8394,10 @@
         <v>36</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>491</v>
+        <v>1228</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="O54" s="9"/>
       <c r="P54" s="1" t="s">
@@ -8417,28 +8440,28 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>36</v>
@@ -8450,61 +8473,61 @@
         <v>36</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>497</v>
+        <v>1192</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="O55" s="9"/>
       <c r="P55" s="1" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="S55" s="1" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U55" s="1" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="V55" s="1" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="X55" s="1" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="Y55" s="1" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="Z55" s="1" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="AA55" s="1" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="AB55" s="1" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>33</v>
@@ -8513,11 +8536,11 @@
         <v>34</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>36</v>
@@ -8529,70 +8552,70 @@
         <v>36</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>509</v>
+        <v>1231</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="O56" s="9"/>
       <c r="P56" s="1" t="s">
-        <v>510</v>
+        <v>476</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>511</v>
+        <v>477</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>511</v>
+        <v>477</v>
       </c>
       <c r="S56" s="1" t="s">
-        <v>511</v>
+        <v>477</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>512</v>
+        <v>478</v>
       </c>
       <c r="V56" s="1" t="s">
-        <v>513</v>
+        <v>479</v>
       </c>
       <c r="W56" s="1" t="s">
-        <v>513</v>
+        <v>479</v>
       </c>
       <c r="X56" s="1" t="s">
-        <v>514</v>
+        <v>480</v>
       </c>
       <c r="Y56" s="1" t="s">
-        <v>515</v>
+        <v>481</v>
       </c>
       <c r="Z56" s="1" t="s">
-        <v>516</v>
+        <v>482</v>
       </c>
       <c r="AA56" s="1" t="s">
-        <v>517</v>
+        <v>483</v>
       </c>
       <c r="AB56" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>518</v>
+        <v>484</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>519</v>
+        <v>485</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>520</v>
+        <v>486</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>521</v>
+        <v>487</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -8606,73 +8629,73 @@
         <v>29</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>522</v>
+        <v>488</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="O57" s="9"/>
       <c r="P57" s="1" t="s">
-        <v>525</v>
+        <v>491</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>526</v>
+        <v>492</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>527</v>
+        <v>493</v>
       </c>
       <c r="S57" s="1" t="s">
-        <v>528</v>
+        <v>494</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U57" s="1" t="s">
         <v>29</v>
       </c>
       <c r="V57" s="1" t="s">
-        <v>529</v>
+        <v>495</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>526</v>
+        <v>492</v>
       </c>
       <c r="X57" s="1" t="s">
-        <v>530</v>
+        <v>496</v>
       </c>
       <c r="Y57" s="1" t="s">
-        <v>531</v>
+        <v>497</v>
       </c>
       <c r="Z57" s="1" t="s">
-        <v>532</v>
+        <v>498</v>
       </c>
       <c r="AA57" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB57" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>533</v>
+        <v>499</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>534</v>
+        <v>500</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>535</v>
+        <v>501</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -8686,70 +8709,70 @@
         <v>36</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>536</v>
+        <v>1241</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>537</v>
+        <v>502</v>
       </c>
       <c r="O58" s="9"/>
       <c r="P58" s="1" t="s">
-        <v>538</v>
+        <v>503</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>539</v>
+        <v>504</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>540</v>
+        <v>505</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="U58" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="V58" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>542</v>
+        <v>507</v>
       </c>
       <c r="X58" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="Z58" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="AA58" s="1" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
       <c r="AB58" s="1" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>544</v>
+        <v>509</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>545</v>
+        <v>510</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>546</v>
+        <v>511</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -8763,77 +8786,77 @@
         <v>36</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>547</v>
+        <v>512</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>548</v>
+        <v>513</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>549</v>
+        <v>514</v>
       </c>
       <c r="O59" s="9"/>
       <c r="P59" s="1" t="s">
-        <v>550</v>
+        <v>515</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>551</v>
+        <v>516</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>552</v>
+        <v>517</v>
       </c>
       <c r="S59" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="U59" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="V59" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>553</v>
+        <v>518</v>
       </c>
       <c r="X59" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="Y59" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="Z59" s="1" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="AA59" s="1" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
       <c r="AB59" s="1" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>555</v>
+        <v>520</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>556</v>
+        <v>521</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I60" s="8" t="s">
         <v>36</v>
@@ -8845,74 +8868,74 @@
         <v>36</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>557</v>
+        <v>522</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>1207</v>
+        <v>1158</v>
       </c>
       <c r="O60" s="9"/>
       <c r="P60" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>558</v>
+        <v>523</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>559</v>
+        <v>524</v>
       </c>
       <c r="S60" s="1" t="s">
-        <v>560</v>
+        <v>525</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U60" s="1" t="s">
-        <v>561</v>
+        <v>526</v>
       </c>
       <c r="V60" s="1" t="s">
-        <v>562</v>
+        <v>527</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>563</v>
+        <v>528</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>564</v>
+        <v>529</v>
       </c>
       <c r="Y60" s="1" t="s">
-        <v>565</v>
+        <v>530</v>
       </c>
       <c r="Z60" s="1" t="s">
-        <v>566</v>
+        <v>531</v>
       </c>
       <c r="AA60" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB60" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>567</v>
+        <v>532</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>568</v>
+        <v>533</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>569</v>
+        <v>534</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>36</v>
@@ -8924,74 +8947,74 @@
         <v>36</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>570</v>
+        <v>1242</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>571</v>
+        <v>535</v>
       </c>
       <c r="O61" s="9"/>
       <c r="P61" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>572</v>
+        <v>536</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>573</v>
+        <v>537</v>
       </c>
       <c r="S61" s="1" t="s">
-        <v>574</v>
+        <v>538</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U61" s="1" t="s">
-        <v>575</v>
+        <v>539</v>
       </c>
       <c r="V61" s="1" t="s">
-        <v>576</v>
+        <v>540</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>577</v>
+        <v>541</v>
       </c>
       <c r="X61" s="1" t="s">
-        <v>578</v>
+        <v>542</v>
       </c>
       <c r="Y61" s="1" t="s">
-        <v>579</v>
+        <v>543</v>
       </c>
       <c r="Z61" s="1" t="s">
-        <v>580</v>
+        <v>544</v>
       </c>
       <c r="AA61" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB61" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>581</v>
+        <v>545</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>582</v>
+        <v>546</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>583</v>
+        <v>547</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>584</v>
+        <v>548</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>36</v>
@@ -9003,38 +9026,38 @@
         <v>36</v>
       </c>
       <c r="L62" s="21" t="s">
-        <v>1210</v>
+        <v>1161</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>1208</v>
+        <v>1159</v>
       </c>
       <c r="O62" s="9"/>
       <c r="P62" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>585</v>
+        <v>549</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>586</v>
+        <v>550</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>587</v>
+        <v>551</v>
       </c>
       <c r="T62" s="1" t="s">
         <v>29</v>
       </c>
       <c r="U62" s="1" t="s">
-        <v>588</v>
+        <v>552</v>
       </c>
       <c r="V62" s="1" t="s">
-        <v>589</v>
+        <v>553</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>590</v>
+        <v>554</v>
       </c>
       <c r="X62" s="1" t="s">
-        <v>591</v>
+        <v>555</v>
       </c>
       <c r="Y62" s="1" t="s">
         <v>29</v>
@@ -9043,34 +9066,34 @@
         <v>29</v>
       </c>
       <c r="AA62" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB62" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>592</v>
+        <v>556</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>593</v>
+        <v>557</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>583</v>
+        <v>547</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>594</v>
+        <v>558</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>36</v>
@@ -9082,10 +9105,10 @@
         <v>36</v>
       </c>
       <c r="L63" s="21" t="s">
-        <v>1211</v>
+        <v>1162</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>1209</v>
+        <v>1160</v>
       </c>
       <c r="O63" s="9"/>
       <c r="P63" s="1" t="s">
@@ -9128,28 +9151,28 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>595</v>
+        <v>559</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>596</v>
+        <v>560</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>597</v>
+        <v>561</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>598</v>
+        <v>562</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I64" s="8" t="s">
         <v>36</v>
@@ -9161,58 +9184,58 @@
         <v>36</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>599</v>
+        <v>563</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>1212</v>
+        <v>1163</v>
       </c>
       <c r="O64" s="9"/>
       <c r="P64" s="1" t="s">
-        <v>600</v>
+        <v>564</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>601</v>
+        <v>565</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>602</v>
+        <v>566</v>
       </c>
       <c r="S64" s="1" t="s">
-        <v>603</v>
+        <v>567</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U64" s="1" t="s">
-        <v>604</v>
+        <v>568</v>
       </c>
       <c r="V64" s="1" t="s">
-        <v>605</v>
+        <v>569</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>605</v>
+        <v>569</v>
       </c>
       <c r="X64" s="1" t="s">
-        <v>606</v>
+        <v>570</v>
       </c>
       <c r="Y64" s="1" t="s">
-        <v>607</v>
+        <v>571</v>
       </c>
       <c r="Z64" s="1" t="s">
-        <v>608</v>
+        <v>572</v>
       </c>
       <c r="AA64" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB64" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="65" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>609</v>
+        <v>573</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>610</v>
+        <v>574</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>32</v>
@@ -9224,11 +9247,11 @@
         <v>52</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>611</v>
+        <v>575</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>36</v>
@@ -9240,26 +9263,26 @@
         <v>36</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>612</v>
+        <v>576</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>613</v>
+        <v>577</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>614</v>
+        <v>578</v>
       </c>
       <c r="O65" s="9"/>
       <c r="P65" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>615</v>
+        <v>579</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>616</v>
+        <v>580</v>
       </c>
       <c r="S65" s="1" t="s">
-        <v>616</v>
+        <v>580</v>
       </c>
       <c r="T65" s="1" t="s">
         <v>29</v>
@@ -9283,34 +9306,34 @@
         <v>29</v>
       </c>
       <c r="AA65" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB65" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>617</v>
+        <v>581</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>618</v>
+        <v>582</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>619</v>
+        <v>583</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I66" s="8" t="s">
         <v>36</v>
@@ -9322,74 +9345,74 @@
         <v>36</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>620</v>
+        <v>1243</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>621</v>
+        <v>584</v>
       </c>
       <c r="O66" s="9"/>
       <c r="P66" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>622</v>
+        <v>585</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>623</v>
+        <v>586</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>623</v>
+        <v>586</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U66" s="1" t="s">
         <v>29</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>623</v>
+        <v>586</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>623</v>
+        <v>586</v>
       </c>
       <c r="X66" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Y66" s="1" t="s">
-        <v>624</v>
+        <v>587</v>
       </c>
       <c r="Z66" s="1" t="s">
         <v>29</v>
       </c>
       <c r="AA66" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB66" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="67" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>625</v>
+        <v>588</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>626</v>
+        <v>589</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>627</v>
+        <v>590</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>36</v>
@@ -9401,58 +9424,58 @@
         <v>36</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>628</v>
+        <v>1244</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>629</v>
+        <v>591</v>
       </c>
       <c r="O67" s="9"/>
       <c r="P67" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>630</v>
+        <v>592</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>631</v>
+        <v>593</v>
       </c>
       <c r="S67" s="1" t="s">
-        <v>632</v>
+        <v>594</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U67" s="1" t="s">
         <v>29</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>633</v>
+        <v>595</v>
       </c>
       <c r="W67" s="1" t="s">
-        <v>634</v>
+        <v>596</v>
       </c>
       <c r="X67" s="1" t="s">
-        <v>635</v>
+        <v>597</v>
       </c>
       <c r="Y67" s="1" t="s">
-        <v>636</v>
+        <v>598</v>
       </c>
       <c r="Z67" s="1" t="s">
         <v>29</v>
       </c>
       <c r="AA67" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB67" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="68" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>637</v>
+        <v>599</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>638</v>
+        <v>600</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>32</v>
@@ -9464,7 +9487,7 @@
         <v>34</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>639</v>
+        <v>601</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -9478,38 +9501,38 @@
         <v>36</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>640</v>
+        <v>602</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>641</v>
+        <v>603</v>
       </c>
       <c r="O68" s="9"/>
       <c r="P68" s="1" t="s">
-        <v>642</v>
+        <v>604</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>643</v>
+        <v>605</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>644</v>
+        <v>606</v>
       </c>
       <c r="S68" s="1" t="s">
-        <v>645</v>
+        <v>607</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U68" s="1" t="s">
         <v>29</v>
       </c>
       <c r="V68" s="1" t="s">
-        <v>646</v>
+        <v>608</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>647</v>
+        <v>609</v>
       </c>
       <c r="X68" s="1" t="s">
-        <v>648</v>
+        <v>610</v>
       </c>
       <c r="Y68" s="1" t="s">
         <v>29</v>
@@ -9518,18 +9541,18 @@
         <v>29</v>
       </c>
       <c r="AA68" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB68" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="69" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>649</v>
+        <v>611</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>650</v>
+        <v>612</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>75</v>
@@ -9541,7 +9564,7 @@
         <v>34</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>651</v>
+        <v>613</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -9555,10 +9578,10 @@
         <v>36</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>652</v>
+        <v>1215</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>653</v>
+        <v>614</v>
       </c>
       <c r="O69" s="9"/>
       <c r="P69" s="1" t="s">
@@ -9586,7 +9609,7 @@
         <v>29</v>
       </c>
       <c r="X69" s="1" t="s">
-        <v>654</v>
+        <v>615</v>
       </c>
       <c r="Y69" s="1" t="s">
         <v>29</v>
@@ -9595,34 +9618,34 @@
         <v>29</v>
       </c>
       <c r="AA69" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB69" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="70" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>655</v>
+        <v>616</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>656</v>
+        <v>617</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>657</v>
+        <v>618</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I70" s="8" t="s">
         <v>36</v>
@@ -9634,10 +9657,10 @@
         <v>36</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>658</v>
+        <v>1245</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>659</v>
+        <v>619</v>
       </c>
       <c r="O70" s="9"/>
       <c r="P70" s="1"/>
@@ -9654,28 +9677,28 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
     </row>
-    <row r="71" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>660</v>
+        <v>620</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>661</v>
+        <v>621</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>662</v>
+        <v>622</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I71" s="8" t="s">
         <v>36</v>
@@ -9687,10 +9710,10 @@
         <v>36</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>663</v>
+        <v>1246</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>664</v>
+        <v>623</v>
       </c>
       <c r="O71" s="9"/>
       <c r="P71" s="1"/>
@@ -9707,15 +9730,15 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
     </row>
-    <row r="72" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>665</v>
+        <v>624</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>666</v>
+        <v>625</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>33</v>
@@ -9724,7 +9747,7 @@
         <v>34</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>667</v>
+        <v>626</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -9738,10 +9761,10 @@
         <v>36</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>668</v>
+        <v>627</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>669</v>
+        <v>628</v>
       </c>
       <c r="O72" s="9"/>
       <c r="P72" s="1" t="s">
@@ -9778,30 +9801,30 @@
         <v>29</v>
       </c>
       <c r="AA72" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB72" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="73" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>670</v>
+        <v>629</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>671</v>
+        <v>630</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>672</v>
+        <v>631</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -9815,74 +9838,74 @@
         <v>36</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>673</v>
+        <v>632</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>674</v>
+        <v>633</v>
       </c>
       <c r="O73" s="9"/>
       <c r="P73" s="1" t="s">
-        <v>675</v>
+        <v>634</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>676</v>
+        <v>635</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>677</v>
+        <v>636</v>
       </c>
       <c r="S73" s="1" t="s">
-        <v>678</v>
+        <v>637</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>679</v>
+        <v>638</v>
       </c>
       <c r="U73" s="1" t="s">
-        <v>680</v>
+        <v>639</v>
       </c>
       <c r="V73" s="1" t="s">
-        <v>681</v>
+        <v>640</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>682</v>
+        <v>641</v>
       </c>
       <c r="X73" s="1" t="s">
-        <v>683</v>
+        <v>642</v>
       </c>
       <c r="Y73" s="1" t="s">
-        <v>684</v>
+        <v>643</v>
       </c>
       <c r="Z73" s="1" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="AA73" s="1" t="s">
-        <v>686</v>
+        <v>645</v>
       </c>
       <c r="AB73" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
-    <row r="74" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>688</v>
+        <v>647</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>689</v>
+        <v>648</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="I74" s="8" t="s">
         <v>36</v>
@@ -9894,61 +9917,61 @@
         <v>36</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>690</v>
+        <v>649</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>691</v>
+        <v>650</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>692</v>
+        <v>651</v>
       </c>
       <c r="O74" s="9"/>
       <c r="P74" s="1" t="s">
-        <v>693</v>
+        <v>652</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>694</v>
+        <v>653</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>695</v>
+        <v>654</v>
       </c>
       <c r="S74" s="1" t="s">
-        <v>696</v>
+        <v>655</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>697</v>
+        <v>656</v>
       </c>
       <c r="U74" s="1" t="s">
-        <v>698</v>
+        <v>657</v>
       </c>
       <c r="V74" s="1" t="s">
-        <v>699</v>
+        <v>658</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>700</v>
+        <v>659</v>
       </c>
       <c r="X74" s="1" t="s">
-        <v>701</v>
+        <v>660</v>
       </c>
       <c r="Y74" s="1" t="s">
-        <v>702</v>
+        <v>661</v>
       </c>
       <c r="Z74" s="1" t="s">
-        <v>703</v>
+        <v>662</v>
       </c>
       <c r="AA74" s="1" t="s">
-        <v>704</v>
+        <v>663</v>
       </c>
       <c r="AB74" s="1" t="s">
-        <v>705</v>
+        <v>664</v>
       </c>
     </row>
-    <row r="75" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>706</v>
+        <v>665</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>1224</v>
+        <v>1172</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>32</v>
@@ -9960,13 +9983,13 @@
         <v>34</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>707</v>
+        <v>666</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I75" s="8" t="s">
         <v>36</v>
@@ -9978,10 +10001,10 @@
         <v>36</v>
       </c>
       <c r="L75" s="21" t="s">
-        <v>1237</v>
+        <v>1183</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>1223</v>
+        <v>1171</v>
       </c>
       <c r="O75" s="9"/>
       <c r="P75" s="1" t="s">
@@ -10024,12 +10047,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="76" spans="1:28" ht="165" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>709</v>
+        <v>668</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1236</v>
+        <v>1182</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>32</v>
@@ -10041,13 +10064,13 @@
         <v>34</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>710</v>
+        <v>669</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I76" s="8" t="s">
         <v>36</v>
@@ -10059,10 +10082,10 @@
         <v>36</v>
       </c>
       <c r="L76" s="21" t="s">
-        <v>1238</v>
+        <v>1184</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>1214</v>
+        <v>1164</v>
       </c>
       <c r="O76" s="9"/>
       <c r="P76" s="1" t="s">
@@ -10105,30 +10128,30 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>711</v>
+        <v>670</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>712</v>
+        <v>671</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>713</v>
+        <v>672</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>714</v>
+        <v>673</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>715</v>
+        <v>674</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I77" s="8" t="s">
         <v>36</v>
@@ -10139,7 +10162,9 @@
       <c r="K77" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L77" s="21"/>
+      <c r="L77" s="21" t="s">
+        <v>1208</v>
+      </c>
       <c r="O77" s="9"/>
       <c r="P77" s="1" t="s">
         <v>29</v>
@@ -10181,15 +10206,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="78" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>716</v>
+        <v>675</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>717</v>
+        <v>676</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>33</v>
@@ -10198,13 +10223,13 @@
         <v>52</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>718</v>
+        <v>677</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>715</v>
+        <v>674</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I78" s="8" t="s">
         <v>36</v>
@@ -10215,7 +10240,9 @@
       <c r="K78" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L78" s="21"/>
+      <c r="L78" s="21" t="s">
+        <v>1207</v>
+      </c>
       <c r="O78" s="9"/>
       <c r="P78" s="1" t="s">
         <v>29</v>
@@ -10259,10 +10286,10 @@
     </row>
     <row r="79" spans="1:28" ht="180" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>719</v>
+        <v>678</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>720</v>
+        <v>679</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>32</v>
@@ -10274,13 +10301,13 @@
         <v>52</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>721</v>
+        <v>680</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I79" s="8" t="s">
         <v>36</v>
@@ -10292,10 +10319,10 @@
         <v>36</v>
       </c>
       <c r="L79" s="21" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>1215</v>
+        <v>1165</v>
       </c>
       <c r="O79" s="9"/>
       <c r="P79" s="1" t="s">
@@ -10338,12 +10365,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="80" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>722</v>
+        <v>681</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1225</v>
+        <v>1173</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>32</v>
@@ -10355,13 +10382,13 @@
         <v>34</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>723</v>
+        <v>682</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I80" s="8" t="s">
         <v>36</v>
@@ -10373,10 +10400,10 @@
         <v>36</v>
       </c>
       <c r="L80" s="21" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>1229</v>
+        <v>1176</v>
       </c>
       <c r="O80" s="9"/>
       <c r="P80" s="1" t="s">
@@ -10419,30 +10446,30 @@
         <v>29</v>
       </c>
     </row>
-    <row r="81" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>724</v>
+        <v>683</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>1226</v>
+        <v>1174</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>725</v>
+        <v>684</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>726</v>
+        <v>685</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I81" s="8" t="s">
         <v>36</v>
@@ -10454,10 +10481,10 @@
         <v>36</v>
       </c>
       <c r="L81" s="21" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>1222</v>
+        <v>1170</v>
       </c>
       <c r="O81" s="9"/>
       <c r="P81" s="1" t="s">
@@ -10500,30 +10527,30 @@
         <v>29</v>
       </c>
     </row>
-    <row r="82" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>727</v>
+        <v>686</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>1227</v>
+        <v>1175</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>728</v>
+        <v>687</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>729</v>
+        <v>688</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I82" s="8" t="s">
         <v>36</v>
@@ -10535,10 +10562,10 @@
         <v>36</v>
       </c>
       <c r="L82" s="21" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>1220</v>
+        <v>1169</v>
       </c>
       <c r="O82" s="9"/>
       <c r="P82" s="1" t="s">
@@ -10581,15 +10608,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="83" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>730</v>
+        <v>689</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>731</v>
+        <v>690</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>33</v>
@@ -10598,13 +10625,13 @@
         <v>34</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>732</v>
+        <v>691</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I83" s="8" t="s">
         <v>36</v>
@@ -10615,7 +10642,9 @@
       <c r="K83" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L83" s="21"/>
+      <c r="L83" s="21" t="s">
+        <v>1224</v>
+      </c>
       <c r="O83" s="9"/>
       <c r="P83" s="1" t="s">
         <v>29</v>
@@ -10657,30 +10686,30 @@
         <v>29</v>
       </c>
     </row>
-    <row r="84" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>733</v>
+        <v>692</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>734</v>
+        <v>693</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>725</v>
+        <v>684</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>735</v>
+        <v>694</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I84" s="8" t="s">
         <v>36</v>
@@ -10691,7 +10720,9 @@
       <c r="K84" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L84" s="21"/>
+      <c r="L84" s="21" t="s">
+        <v>1225</v>
+      </c>
       <c r="O84" s="9"/>
       <c r="P84" s="1" t="s">
         <v>29</v>
@@ -10733,30 +10764,30 @@
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:28" ht="189" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" ht="189" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>736</v>
+        <v>695</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>737</v>
+        <v>696</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>738</v>
+        <v>697</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>36</v>
@@ -10768,38 +10799,38 @@
         <v>36</v>
       </c>
       <c r="L85" s="21" t="s">
-        <v>1217</v>
+        <v>1167</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>1218</v>
+        <v>1168</v>
       </c>
       <c r="O85" s="9"/>
       <c r="P85" s="1" t="s">
-        <v>739</v>
+        <v>698</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>740</v>
+        <v>699</v>
       </c>
       <c r="R85" s="1" t="s">
-        <v>741</v>
+        <v>700</v>
       </c>
       <c r="S85" s="1" t="s">
-        <v>742</v>
+        <v>701</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>743</v>
+        <v>702</v>
       </c>
       <c r="U85" s="1" t="s">
         <v>29</v>
       </c>
       <c r="V85" s="1" t="s">
-        <v>744</v>
+        <v>703</v>
       </c>
       <c r="W85" s="1" t="s">
-        <v>745</v>
+        <v>704</v>
       </c>
       <c r="X85" s="1" t="s">
-        <v>746</v>
+        <v>705</v>
       </c>
       <c r="Y85" s="1" t="s">
         <v>29</v>
@@ -10808,30 +10839,30 @@
         <v>29</v>
       </c>
       <c r="AA85" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB85" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="86" spans="1:28" ht="200.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" ht="200.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>747</v>
+        <v>706</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>748</v>
+        <v>707</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>520</v>
+        <v>486</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>749</v>
+        <v>708</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
@@ -10845,61 +10876,61 @@
         <v>36</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>1239</v>
+        <v>1185</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>1216</v>
+        <v>1166</v>
       </c>
       <c r="O86" s="9"/>
       <c r="P86" s="1" t="s">
-        <v>750</v>
+        <v>709</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>751</v>
+        <v>710</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>752</v>
+        <v>711</v>
       </c>
       <c r="S86" s="1" t="s">
-        <v>753</v>
+        <v>712</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>754</v>
+        <v>713</v>
       </c>
       <c r="U86" s="1" t="s">
         <v>29</v>
       </c>
       <c r="V86" s="1" t="s">
-        <v>755</v>
+        <v>714</v>
       </c>
       <c r="W86" s="1" t="s">
-        <v>756</v>
+        <v>715</v>
       </c>
       <c r="X86" s="1" t="s">
-        <v>757</v>
+        <v>716</v>
       </c>
       <c r="Y86" s="1" t="s">
-        <v>758</v>
+        <v>717</v>
       </c>
       <c r="Z86" s="1" t="s">
         <v>29</v>
       </c>
       <c r="AA86" s="1" t="s">
-        <v>759</v>
+        <v>718</v>
       </c>
       <c r="AB86" s="1" t="s">
-        <v>760</v>
+        <v>719</v>
       </c>
     </row>
-    <row r="87" spans="1:28" ht="180" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>761</v>
+        <v>720</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>762</v>
+        <v>721</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>33</v>
@@ -10908,7 +10939,7 @@
         <v>34</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>763</v>
+        <v>722</v>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -10922,58 +10953,58 @@
         <v>29</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>764</v>
+        <v>723</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>669</v>
+        <v>628</v>
       </c>
       <c r="O87" s="9"/>
       <c r="P87" s="1" t="s">
-        <v>765</v>
+        <v>724</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>766</v>
+        <v>725</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>767</v>
+        <v>726</v>
       </c>
       <c r="S87" s="1" t="s">
-        <v>768</v>
+        <v>727</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>769</v>
+        <v>728</v>
       </c>
       <c r="U87" s="1" t="s">
-        <v>770</v>
+        <v>729</v>
       </c>
       <c r="V87" s="1" t="s">
-        <v>771</v>
+        <v>730</v>
       </c>
       <c r="W87" s="1" t="s">
-        <v>772</v>
+        <v>731</v>
       </c>
       <c r="X87" s="1" t="s">
-        <v>773</v>
+        <v>732</v>
       </c>
       <c r="Y87" s="1" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="Z87" s="1" t="s">
-        <v>775</v>
+        <v>734</v>
       </c>
       <c r="AA87" s="1" t="s">
-        <v>776</v>
+        <v>735</v>
       </c>
       <c r="AB87" s="1" t="s">
-        <v>776</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="88" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>777</v>
+        <v>736</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>778</v>
+        <v>737</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>75</v>
@@ -10985,7 +11016,7 @@
         <v>34</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>779</v>
+        <v>738</v>
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
@@ -10999,13 +11030,13 @@
         <v>36</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>780</v>
+        <v>1214</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>781</v>
+        <v>739</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>782</v>
+        <v>740</v>
       </c>
       <c r="O88" s="9"/>
       <c r="P88" s="1" t="s">
@@ -11048,12 +11079,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="89" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" ht="66" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>783</v>
+        <v>741</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>784</v>
+        <v>742</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>75</v>
@@ -11062,10 +11093,10 @@
         <v>32</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>785</v>
+        <v>743</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>786</v>
+        <v>744</v>
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
@@ -11079,58 +11110,58 @@
         <v>36</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>787</v>
+        <v>1236</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>788</v>
+        <v>745</v>
       </c>
       <c r="O89" s="9"/>
       <c r="P89" s="1" t="s">
-        <v>789</v>
+        <v>746</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>790</v>
+        <v>747</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>791</v>
+        <v>748</v>
       </c>
       <c r="S89" s="1" t="s">
-        <v>792</v>
+        <v>749</v>
       </c>
       <c r="T89" s="1" t="s">
-        <v>793</v>
+        <v>750</v>
       </c>
       <c r="U89" s="1" t="s">
-        <v>794</v>
+        <v>751</v>
       </c>
       <c r="V89" s="1" t="s">
-        <v>795</v>
+        <v>752</v>
       </c>
       <c r="W89" s="1" t="s">
-        <v>796</v>
+        <v>753</v>
       </c>
       <c r="X89" s="1" t="s">
-        <v>797</v>
+        <v>754</v>
       </c>
       <c r="Y89" s="1" t="s">
-        <v>798</v>
+        <v>755</v>
       </c>
       <c r="Z89" s="1" t="s">
-        <v>799</v>
+        <v>756</v>
       </c>
       <c r="AA89" s="1" t="s">
-        <v>800</v>
+        <v>757</v>
       </c>
       <c r="AB89" s="1" t="s">
-        <v>800</v>
+        <v>757</v>
       </c>
     </row>
-    <row r="90" spans="1:28" ht="165" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>801</v>
+        <v>758</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>802</v>
+        <v>759</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>75</v>
@@ -11139,10 +11170,10 @@
         <v>32</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>803</v>
+        <v>760</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>804</v>
+        <v>761</v>
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
@@ -11156,10 +11187,10 @@
         <v>29</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>805</v>
+        <v>762</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>806</v>
+        <v>763</v>
       </c>
       <c r="O90" s="9"/>
       <c r="P90" s="1" t="s">
@@ -11169,7 +11200,7 @@
         <v>75</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>807</v>
+        <v>764</v>
       </c>
       <c r="S90" s="1" t="s">
         <v>75</v>
@@ -11196,18 +11227,18 @@
         <v>75</v>
       </c>
       <c r="AA90" s="1" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
       <c r="AB90" s="1" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
     </row>
-    <row r="91" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" ht="76.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>808</v>
+        <v>765</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>809</v>
+        <v>766</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>75</v>
@@ -11219,7 +11250,7 @@
         <v>34</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>810</v>
+        <v>767</v>
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -11233,20 +11264,20 @@
         <v>36</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>811</v>
+        <v>768</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>812</v>
+        <v>769</v>
       </c>
       <c r="O91" s="9"/>
       <c r="P91" s="1" t="s">
-        <v>813</v>
+        <v>770</v>
       </c>
       <c r="Q91" s="1" t="s">
-        <v>814</v>
+        <v>771</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>815</v>
+        <v>772</v>
       </c>
       <c r="S91" s="1" t="s">
         <v>75</v>
@@ -11261,7 +11292,7 @@
         <v>75</v>
       </c>
       <c r="W91" s="1" t="s">
-        <v>816</v>
+        <v>773</v>
       </c>
       <c r="X91" s="1" t="s">
         <v>75</v>
@@ -11273,16 +11304,16 @@
         <v>75</v>
       </c>
       <c r="AA91" s="1" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
       <c r="AB91" s="1" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
     </row>
-    <row r="92" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:28" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:28" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>817</v>
+        <v>774</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -11313,12 +11344,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="94" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>818</v>
+        <v>775</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>819</v>
+        <v>776</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>32</v>
@@ -11330,11 +11361,11 @@
         <v>34</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>820</v>
+        <v>777</v>
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I94" s="8" t="s">
         <v>36</v>
@@ -11346,58 +11377,58 @@
         <v>36</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>821</v>
+        <v>778</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>822</v>
+        <v>779</v>
       </c>
       <c r="O94" s="9"/>
       <c r="P94" s="1" t="s">
-        <v>823</v>
+        <v>780</v>
       </c>
       <c r="Q94" s="1" t="s">
-        <v>824</v>
+        <v>781</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>825</v>
+        <v>782</v>
       </c>
       <c r="S94" s="1" t="s">
-        <v>826</v>
+        <v>783</v>
       </c>
       <c r="T94" s="1" t="s">
-        <v>827</v>
+        <v>784</v>
       </c>
       <c r="U94" s="1" t="s">
-        <v>828</v>
+        <v>785</v>
       </c>
       <c r="V94" s="1" t="s">
-        <v>829</v>
+        <v>786</v>
       </c>
       <c r="W94" s="1" t="s">
-        <v>830</v>
+        <v>787</v>
       </c>
       <c r="X94" s="1" t="s">
-        <v>831</v>
+        <v>788</v>
       </c>
       <c r="Y94" s="1" t="s">
-        <v>832</v>
+        <v>789</v>
       </c>
       <c r="Z94" s="1" t="s">
-        <v>833</v>
+        <v>790</v>
       </c>
       <c r="AA94" s="1" t="s">
-        <v>834</v>
+        <v>791</v>
       </c>
       <c r="AB94" s="1" t="s">
-        <v>835</v>
+        <v>792</v>
       </c>
     </row>
-    <row r="95" spans="1:28" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" ht="123.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>836</v>
+        <v>793</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>837</v>
+        <v>794</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>32</v>
@@ -11409,11 +11440,11 @@
         <v>34</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>838</v>
+        <v>795</v>
       </c>
       <c r="G95" s="1"/>
       <c r="H95" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I95" s="8" t="s">
         <v>36</v>
@@ -11425,58 +11456,58 @@
         <v>36</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>839</v>
+        <v>796</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>840</v>
+        <v>797</v>
       </c>
       <c r="O95" s="9"/>
       <c r="P95" s="1" t="s">
-        <v>841</v>
+        <v>798</v>
       </c>
       <c r="Q95" s="1" t="s">
-        <v>842</v>
+        <v>799</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>843</v>
+        <v>800</v>
       </c>
       <c r="S95" s="1" t="s">
-        <v>844</v>
+        <v>801</v>
       </c>
       <c r="T95" s="1" t="s">
-        <v>845</v>
+        <v>802</v>
       </c>
       <c r="U95" s="1" t="s">
-        <v>846</v>
+        <v>803</v>
       </c>
       <c r="V95" s="1" t="s">
-        <v>847</v>
+        <v>804</v>
       </c>
       <c r="W95" s="1" t="s">
-        <v>848</v>
+        <v>805</v>
       </c>
       <c r="X95" s="1" t="s">
-        <v>849</v>
+        <v>806</v>
       </c>
       <c r="Y95" s="1" t="s">
-        <v>850</v>
+        <v>807</v>
       </c>
       <c r="Z95" s="1" t="s">
-        <v>851</v>
+        <v>808</v>
       </c>
       <c r="AA95" s="1" t="s">
-        <v>852</v>
+        <v>809</v>
       </c>
       <c r="AB95" s="1" t="s">
-        <v>853</v>
+        <v>810</v>
       </c>
     </row>
-    <row r="96" spans="1:28" ht="279" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" ht="279" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>854</v>
+        <v>811</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>1230</v>
+        <v>1177</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>32</v>
@@ -11485,16 +11516,16 @@
         <v>33</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>855</v>
+        <v>812</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I96" s="8" t="s">
         <v>36</v>
@@ -11506,13 +11537,13 @@
         <v>36</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>856</v>
+        <v>813</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>857</v>
+        <v>814</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>858</v>
+        <v>815</v>
       </c>
       <c r="O96" s="9"/>
       <c r="P96" s="1"/>
@@ -11529,12 +11560,12 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
     </row>
-    <row r="97" spans="1:28" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:28" ht="159.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>859</v>
+        <v>816</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>860</v>
+        <v>817</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>32</v>
@@ -11546,7 +11577,7 @@
         <v>34</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>861</v>
+        <v>818</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
@@ -11560,70 +11591,70 @@
         <v>36</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>1240</v>
+        <v>1186</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>862</v>
+        <v>819</v>
       </c>
       <c r="O97" s="9"/>
       <c r="P97" s="1" t="s">
-        <v>863</v>
+        <v>820</v>
       </c>
       <c r="Q97" s="1" t="s">
-        <v>864</v>
+        <v>821</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>865</v>
+        <v>822</v>
       </c>
       <c r="S97" s="1" t="s">
-        <v>866</v>
+        <v>823</v>
       </c>
       <c r="T97" s="1" t="s">
-        <v>867</v>
+        <v>824</v>
       </c>
       <c r="U97" s="1" t="s">
-        <v>868</v>
+        <v>825</v>
       </c>
       <c r="V97" s="1" t="s">
-        <v>869</v>
+        <v>826</v>
       </c>
       <c r="W97" s="1" t="s">
-        <v>870</v>
+        <v>827</v>
       </c>
       <c r="X97" s="1" t="s">
-        <v>871</v>
+        <v>828</v>
       </c>
       <c r="Y97" s="1" t="s">
-        <v>872</v>
+        <v>829</v>
       </c>
       <c r="Z97" s="1" t="s">
-        <v>873</v>
+        <v>830</v>
       </c>
       <c r="AA97" s="1" t="s">
-        <v>874</v>
+        <v>831</v>
       </c>
       <c r="AB97" s="1" t="s">
-        <v>875</v>
+        <v>832</v>
       </c>
     </row>
-    <row r="98" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:28" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>876</v>
+        <v>833</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>877</v>
+        <v>834</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>878</v>
+        <v>835</v>
       </c>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
@@ -11637,38 +11668,38 @@
         <v>36</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>879</v>
+        <v>1216</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>880</v>
+        <v>836</v>
       </c>
       <c r="O98" s="9"/>
       <c r="P98" s="1" t="s">
-        <v>881</v>
+        <v>837</v>
       </c>
       <c r="Q98" s="1" t="s">
-        <v>882</v>
+        <v>838</v>
       </c>
       <c r="R98" s="1" t="s">
-        <v>883</v>
+        <v>839</v>
       </c>
       <c r="S98" s="1" t="s">
-        <v>884</v>
+        <v>840</v>
       </c>
       <c r="T98" s="1" t="s">
         <v>29</v>
       </c>
       <c r="U98" s="1" t="s">
-        <v>885</v>
+        <v>841</v>
       </c>
       <c r="V98" s="1" t="s">
-        <v>886</v>
+        <v>842</v>
       </c>
       <c r="W98" s="1" t="s">
-        <v>647</v>
+        <v>609</v>
       </c>
       <c r="X98" s="1" t="s">
-        <v>887</v>
+        <v>843</v>
       </c>
       <c r="Y98" s="1" t="s">
         <v>29</v>
@@ -11677,21 +11708,21 @@
         <v>29</v>
       </c>
       <c r="AA98" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB98" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="99" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:28" ht="2.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>888</v>
+        <v>844</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>889</v>
+        <v>845</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>33</v>
@@ -11700,7 +11731,7 @@
         <v>34</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>890</v>
+        <v>846</v>
       </c>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
@@ -11714,17 +11745,17 @@
         <v>36</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>892</v>
+        <v>848</v>
       </c>
       <c r="O99" s="9"/>
       <c r="P99" s="1" t="s">
-        <v>893</v>
+        <v>849</v>
       </c>
       <c r="Q99" s="1" t="s">
-        <v>894</v>
+        <v>850</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>29</v>
@@ -11736,36 +11767,36 @@
         <v>29</v>
       </c>
       <c r="U99" s="1" t="s">
-        <v>895</v>
+        <v>851</v>
       </c>
       <c r="V99" s="1" t="s">
-        <v>896</v>
+        <v>852</v>
       </c>
       <c r="W99" s="1" t="s">
-        <v>647</v>
+        <v>609</v>
       </c>
       <c r="X99" s="1" t="s">
-        <v>897</v>
+        <v>853</v>
       </c>
       <c r="Y99" s="1" t="s">
-        <v>898</v>
+        <v>854</v>
       </c>
       <c r="Z99" s="1" t="s">
-        <v>898</v>
+        <v>854</v>
       </c>
       <c r="AA99" s="1" t="s">
-        <v>899</v>
+        <v>855</v>
       </c>
       <c r="AB99" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="100" spans="1:28" ht="227.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:28" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>900</v>
+        <v>856</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>901</v>
+        <v>857</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>32</v>
@@ -11777,7 +11808,7 @@
         <v>34</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>902</v>
+        <v>858</v>
       </c>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
@@ -11791,58 +11822,58 @@
         <v>36</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>903</v>
+        <v>859</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>904</v>
+        <v>860</v>
       </c>
       <c r="O100" s="9"/>
       <c r="P100" s="1" t="s">
-        <v>905</v>
+        <v>861</v>
       </c>
       <c r="Q100" s="1" t="s">
-        <v>906</v>
+        <v>862</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>907</v>
+        <v>863</v>
       </c>
       <c r="S100" s="1" t="s">
-        <v>908</v>
+        <v>864</v>
       </c>
       <c r="T100" s="1" t="s">
-        <v>909</v>
+        <v>865</v>
       </c>
       <c r="U100" s="1" t="s">
-        <v>910</v>
+        <v>866</v>
       </c>
       <c r="V100" s="1" t="s">
-        <v>911</v>
+        <v>867</v>
       </c>
       <c r="W100" s="1" t="s">
-        <v>912</v>
+        <v>868</v>
       </c>
       <c r="X100" s="1" t="s">
-        <v>913</v>
+        <v>869</v>
       </c>
       <c r="Y100" s="1" t="s">
-        <v>914</v>
+        <v>870</v>
       </c>
       <c r="Z100" s="1" t="s">
-        <v>915</v>
+        <v>871</v>
       </c>
       <c r="AA100" s="1" t="s">
-        <v>916</v>
+        <v>872</v>
       </c>
       <c r="AB100" s="1" t="s">
-        <v>917</v>
+        <v>873</v>
       </c>
     </row>
-    <row r="101" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:28" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>918</v>
+        <v>874</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>919</v>
+        <v>875</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>75</v>
@@ -11851,10 +11882,10 @@
         <v>32</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>520</v>
+        <v>486</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>920</v>
+        <v>876</v>
       </c>
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
@@ -11868,70 +11899,70 @@
         <v>29</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>921</v>
+        <v>877</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>922</v>
+        <v>878</v>
       </c>
       <c r="O101" s="9"/>
       <c r="P101" s="1" t="s">
-        <v>923</v>
+        <v>879</v>
       </c>
       <c r="Q101" s="1" t="s">
-        <v>772</v>
+        <v>731</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>924</v>
+        <v>880</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>925</v>
+        <v>881</v>
       </c>
       <c r="T101" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U101" s="1" t="s">
         <v>29</v>
       </c>
       <c r="V101" s="1" t="s">
-        <v>926</v>
+        <v>882</v>
       </c>
       <c r="W101" s="1" t="s">
-        <v>772</v>
+        <v>731</v>
       </c>
       <c r="X101" s="1" t="s">
-        <v>927</v>
+        <v>883</v>
       </c>
       <c r="Y101" s="1" t="s">
-        <v>928</v>
+        <v>884</v>
       </c>
       <c r="Z101" s="1" t="s">
-        <v>929</v>
+        <v>885</v>
       </c>
       <c r="AA101" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB101" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="102" spans="1:28" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:28" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>930</v>
+        <v>886</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>931</v>
+        <v>887</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>932</v>
+        <v>888</v>
       </c>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
@@ -11945,58 +11976,58 @@
         <v>36</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>933</v>
+        <v>889</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>934</v>
+        <v>890</v>
       </c>
       <c r="O102" s="9"/>
       <c r="P102" s="1" t="s">
-        <v>935</v>
+        <v>891</v>
       </c>
       <c r="Q102" s="1" t="s">
-        <v>936</v>
+        <v>892</v>
       </c>
       <c r="R102" s="1" t="s">
-        <v>937</v>
+        <v>893</v>
       </c>
       <c r="S102" s="1" t="s">
-        <v>938</v>
+        <v>894</v>
       </c>
       <c r="T102" s="1" t="s">
-        <v>939</v>
+        <v>895</v>
       </c>
       <c r="U102" s="1" t="s">
-        <v>940</v>
+        <v>896</v>
       </c>
       <c r="V102" s="1" t="s">
-        <v>941</v>
+        <v>897</v>
       </c>
       <c r="W102" s="1" t="s">
-        <v>942</v>
+        <v>898</v>
       </c>
       <c r="X102" s="1" t="s">
-        <v>943</v>
+        <v>899</v>
       </c>
       <c r="Y102" s="1" t="s">
-        <v>944</v>
+        <v>900</v>
       </c>
       <c r="Z102" s="1" t="s">
-        <v>945</v>
+        <v>901</v>
       </c>
       <c r="AA102" s="1" t="s">
-        <v>946</v>
+        <v>902</v>
       </c>
       <c r="AB102" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
-    <row r="103" spans="1:28" ht="180" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:28" ht="180" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>947</v>
+        <v>903</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>948</v>
+        <v>904</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>32</v>
@@ -12008,7 +12039,7 @@
         <v>34</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>949</v>
+        <v>905</v>
       </c>
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
@@ -12022,74 +12053,74 @@
         <v>36</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>950</v>
+        <v>906</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>951</v>
+        <v>907</v>
       </c>
       <c r="O103" s="9"/>
       <c r="P103" s="1" t="s">
-        <v>952</v>
+        <v>908</v>
       </c>
       <c r="Q103" s="1" t="s">
-        <v>953</v>
+        <v>909</v>
       </c>
       <c r="R103" s="1" t="s">
-        <v>954</v>
+        <v>910</v>
       </c>
       <c r="S103" s="1" t="s">
-        <v>955</v>
+        <v>911</v>
       </c>
       <c r="T103" s="1" t="s">
-        <v>956</v>
+        <v>912</v>
       </c>
       <c r="U103" s="1" t="s">
-        <v>957</v>
+        <v>913</v>
       </c>
       <c r="V103" s="1" t="s">
-        <v>958</v>
+        <v>914</v>
       </c>
       <c r="W103" s="1" t="s">
-        <v>959</v>
+        <v>915</v>
       </c>
       <c r="X103" s="1" t="s">
-        <v>960</v>
+        <v>916</v>
       </c>
       <c r="Y103" s="1" t="s">
-        <v>961</v>
+        <v>917</v>
       </c>
       <c r="Z103" s="1" t="s">
-        <v>962</v>
+        <v>918</v>
       </c>
       <c r="AA103" s="1" t="s">
-        <v>963</v>
+        <v>919</v>
       </c>
       <c r="AB103" s="1" t="s">
-        <v>964</v>
+        <v>920</v>
       </c>
     </row>
-    <row r="104" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>965</v>
+        <v>921</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>966</v>
+        <v>922</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>967</v>
+        <v>923</v>
       </c>
       <c r="G104" s="1"/>
       <c r="H104" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I104" s="8" t="s">
         <v>36</v>
@@ -12101,38 +12132,38 @@
         <v>36</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>968</v>
+        <v>924</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="O104" s="9"/>
       <c r="P104" s="1" t="s">
-        <v>970</v>
+        <v>926</v>
       </c>
       <c r="Q104" s="1" t="s">
-        <v>971</v>
+        <v>927</v>
       </c>
       <c r="R104" s="1" t="s">
-        <v>972</v>
+        <v>928</v>
       </c>
       <c r="S104" s="1" t="s">
-        <v>973</v>
+        <v>929</v>
       </c>
       <c r="T104" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U104" s="1" t="s">
-        <v>974</v>
+        <v>930</v>
       </c>
       <c r="V104" s="1" t="s">
-        <v>975</v>
+        <v>931</v>
       </c>
       <c r="W104" s="1" t="s">
-        <v>976</v>
+        <v>932</v>
       </c>
       <c r="X104" s="1" t="s">
-        <v>977</v>
+        <v>933</v>
       </c>
       <c r="Y104" s="1" t="s">
         <v>29</v>
@@ -12141,18 +12172,18 @@
         <v>29</v>
       </c>
       <c r="AA104" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB104" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="105" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>978</v>
+        <v>934</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>979</v>
+        <v>935</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>32</v>
@@ -12161,16 +12192,16 @@
         <v>33</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>980</v>
+        <v>936</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>981</v>
+        <v>937</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="I105" s="8" t="s">
         <v>36</v>
@@ -12182,61 +12213,61 @@
         <v>36</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>982</v>
+        <v>938</v>
       </c>
       <c r="M105" s="1" t="s">
-        <v>857</v>
+        <v>814</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>983</v>
+        <v>939</v>
       </c>
       <c r="O105" s="9"/>
       <c r="P105" s="1" t="s">
-        <v>984</v>
+        <v>940</v>
       </c>
       <c r="Q105" s="1" t="s">
-        <v>985</v>
+        <v>941</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>986</v>
+        <v>942</v>
       </c>
       <c r="S105" s="1" t="s">
-        <v>987</v>
+        <v>943</v>
       </c>
       <c r="T105" s="1" t="s">
-        <v>988</v>
+        <v>944</v>
       </c>
       <c r="U105" s="1" t="s">
-        <v>989</v>
+        <v>945</v>
       </c>
       <c r="V105" s="1" t="s">
-        <v>990</v>
+        <v>946</v>
       </c>
       <c r="W105" s="1" t="s">
-        <v>991</v>
+        <v>947</v>
       </c>
       <c r="X105" s="1" t="s">
-        <v>992</v>
+        <v>948</v>
       </c>
       <c r="Y105" s="1" t="s">
-        <v>993</v>
+        <v>949</v>
       </c>
       <c r="Z105" s="1" t="s">
-        <v>993</v>
+        <v>949</v>
       </c>
       <c r="AA105" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB105" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="106" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>994</v>
+        <v>950</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>995</v>
+        <v>951</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>32</v>
@@ -12248,13 +12279,13 @@
         <v>34</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>996</v>
+        <v>952</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="I106" s="8" t="s">
         <v>36</v>
@@ -12266,41 +12297,41 @@
         <v>36</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>997</v>
+        <v>953</v>
       </c>
       <c r="M106" s="1" t="s">
-        <v>998</v>
+        <v>954</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>999</v>
+        <v>955</v>
       </c>
       <c r="O106" s="9"/>
       <c r="P106" s="1" t="s">
-        <v>1000</v>
+        <v>956</v>
       </c>
       <c r="Q106" s="1" t="s">
-        <v>1001</v>
+        <v>957</v>
       </c>
       <c r="R106" s="1" t="s">
-        <v>1002</v>
+        <v>958</v>
       </c>
       <c r="S106" s="1" t="s">
-        <v>1003</v>
+        <v>959</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>1004</v>
+        <v>960</v>
       </c>
       <c r="U106" s="1" t="s">
-        <v>1005</v>
+        <v>961</v>
       </c>
       <c r="V106" s="1" t="s">
-        <v>1006</v>
+        <v>962</v>
       </c>
       <c r="W106" s="1" t="s">
-        <v>634</v>
+        <v>596</v>
       </c>
       <c r="X106" s="1" t="s">
-        <v>1007</v>
+        <v>963</v>
       </c>
       <c r="Y106" s="1" t="s">
         <v>29</v>
@@ -12309,18 +12340,18 @@
         <v>29</v>
       </c>
       <c r="AA106" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB106" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="107" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>1008</v>
+        <v>964</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>1009</v>
+        <v>965</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>32</v>
@@ -12332,13 +12363,13 @@
         <v>34</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>1010</v>
+        <v>966</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="I107" s="8" t="s">
         <v>36</v>
@@ -12350,41 +12381,41 @@
         <v>36</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>1011</v>
+        <v>967</v>
       </c>
       <c r="M107" s="1" t="s">
-        <v>857</v>
+        <v>814</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>1012</v>
+        <v>968</v>
       </c>
       <c r="O107" s="9"/>
       <c r="P107" s="1" t="s">
-        <v>1013</v>
+        <v>969</v>
       </c>
       <c r="Q107" s="1" t="s">
-        <v>1014</v>
+        <v>970</v>
       </c>
       <c r="R107" s="1" t="s">
-        <v>1015</v>
+        <v>971</v>
       </c>
       <c r="S107" s="1" t="s">
-        <v>1016</v>
+        <v>972</v>
       </c>
       <c r="T107" s="1" t="s">
-        <v>1017</v>
+        <v>973</v>
       </c>
       <c r="U107" s="1" t="s">
-        <v>1018</v>
+        <v>974</v>
       </c>
       <c r="V107" s="1" t="s">
-        <v>1019</v>
+        <v>975</v>
       </c>
       <c r="W107" s="1" t="s">
-        <v>1020</v>
+        <v>976</v>
       </c>
       <c r="X107" s="1" t="s">
-        <v>1021</v>
+        <v>977</v>
       </c>
       <c r="Y107" s="1" t="s">
         <v>29</v>
@@ -12393,18 +12424,18 @@
         <v>29</v>
       </c>
       <c r="AA107" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB107" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="108" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:28" ht="99.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>1022</v>
+        <v>978</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1023</v>
+        <v>979</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>32</v>
@@ -12416,11 +12447,11 @@
         <v>34</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>1024</v>
+        <v>980</v>
       </c>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I108" s="8" t="s">
         <v>36</v>
@@ -12432,10 +12463,10 @@
         <v>36</v>
       </c>
       <c r="L108" s="21" t="s">
-        <v>1231</v>
+        <v>1178</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>1232</v>
+        <v>1179</v>
       </c>
       <c r="O108" s="9"/>
       <c r="P108" s="1" t="s">
@@ -12478,24 +12509,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="109" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:28" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>1025</v>
+        <v>981</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>1026</v>
+        <v>982</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>1027</v>
+        <v>983</v>
       </c>
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
@@ -12509,38 +12540,38 @@
         <v>36</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>1028</v>
+        <v>984</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>1029</v>
+        <v>985</v>
       </c>
       <c r="O109" s="9"/>
       <c r="P109" s="1" t="s">
-        <v>1030</v>
+        <v>986</v>
       </c>
       <c r="Q109" s="1" t="s">
-        <v>1031</v>
+        <v>987</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>1032</v>
+        <v>988</v>
       </c>
       <c r="S109" s="1" t="s">
-        <v>1033</v>
+        <v>989</v>
       </c>
       <c r="T109" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U109" s="1" t="s">
-        <v>1034</v>
+        <v>990</v>
       </c>
       <c r="V109" s="1" t="s">
-        <v>1035</v>
+        <v>991</v>
       </c>
       <c r="W109" s="1" t="s">
-        <v>1036</v>
+        <v>992</v>
       </c>
       <c r="X109" s="1" t="s">
-        <v>1037</v>
+        <v>993</v>
       </c>
       <c r="Y109" s="1" t="s">
         <v>29</v>
@@ -12549,30 +12580,30 @@
         <v>29</v>
       </c>
       <c r="AA109" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB109" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="110" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>1038</v>
+        <v>994</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>1039</v>
+        <v>995</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>1040</v>
+        <v>996</v>
       </c>
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
@@ -12586,56 +12617,56 @@
         <v>36</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>1041</v>
+        <v>1201</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>1042</v>
+        <v>997</v>
       </c>
       <c r="O110" s="9"/>
       <c r="P110" s="1" t="s">
-        <v>1043</v>
+        <v>998</v>
       </c>
       <c r="Q110" s="1" t="s">
-        <v>1044</v>
+        <v>999</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>1045</v>
+        <v>1000</v>
       </c>
       <c r="S110" s="1" t="s">
-        <v>1046</v>
+        <v>1001</v>
       </c>
       <c r="T110" s="1" t="s">
-        <v>1047</v>
+        <v>1002</v>
       </c>
       <c r="U110" s="1" t="s">
-        <v>1048</v>
+        <v>1003</v>
       </c>
       <c r="V110" s="1" t="s">
-        <v>1049</v>
+        <v>1004</v>
       </c>
       <c r="W110" s="1" t="s">
-        <v>1050</v>
+        <v>1005</v>
       </c>
       <c r="X110" s="1" t="s">
-        <v>1051</v>
+        <v>1006</v>
       </c>
       <c r="Y110" s="1" t="s">
-        <v>1052</v>
+        <v>1007</v>
       </c>
       <c r="Z110" s="1" t="s">
-        <v>1053</v>
+        <v>1008</v>
       </c>
       <c r="AA110" s="1" t="s">
-        <v>1054</v>
+        <v>1009</v>
       </c>
       <c r="AB110" s="1" t="s">
-        <v>1055</v>
+        <v>1010</v>
       </c>
     </row>
-    <row r="111" spans="1:28" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:28" ht="8.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:28" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>1056</v>
+        <v>1011</v>
       </c>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -12666,24 +12697,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="165" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>1057</v>
+        <v>1012</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>1058</v>
+        <v>1013</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>1059</v>
+        <v>1014</v>
       </c>
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
@@ -12697,61 +12728,61 @@
         <v>36</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>1060</v>
+        <v>1199</v>
       </c>
       <c r="M113" s="1" t="s">
-        <v>1061</v>
+        <v>1015</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>1062</v>
+        <v>1016</v>
       </c>
       <c r="O113" s="9"/>
       <c r="P113" s="1" t="s">
-        <v>1063</v>
+        <v>1017</v>
       </c>
       <c r="Q113" s="1" t="s">
-        <v>1064</v>
+        <v>1018</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>1065</v>
+        <v>1019</v>
       </c>
       <c r="S113" s="1" t="s">
-        <v>1066</v>
+        <v>1020</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>1067</v>
+        <v>1021</v>
       </c>
       <c r="U113" s="1" t="s">
-        <v>1068</v>
+        <v>1022</v>
       </c>
       <c r="V113" s="1" t="s">
-        <v>1069</v>
+        <v>1023</v>
       </c>
       <c r="W113" s="1" t="s">
-        <v>1070</v>
+        <v>1024</v>
       </c>
       <c r="X113" s="1" t="s">
-        <v>1071</v>
+        <v>1025</v>
       </c>
       <c r="Y113" s="1" t="s">
-        <v>1072</v>
+        <v>1026</v>
       </c>
       <c r="Z113" s="1" t="s">
-        <v>1073</v>
+        <v>1027</v>
       </c>
       <c r="AA113" s="1" t="s">
-        <v>1074</v>
+        <v>1028</v>
       </c>
       <c r="AB113" s="1" t="s">
-        <v>1074</v>
+        <v>1028</v>
       </c>
     </row>
-    <row r="114" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>1075</v>
+        <v>1029</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>1076</v>
+        <v>1030</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>32</v>
@@ -12763,11 +12794,11 @@
         <v>34</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>1077</v>
+        <v>1031</v>
       </c>
       <c r="G114" s="1"/>
       <c r="H114" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="I114" s="8" t="s">
         <v>36</v>
@@ -12779,74 +12810,74 @@
         <v>36</v>
       </c>
       <c r="L114" s="21" t="s">
-        <v>1233</v>
+        <v>1200</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>1234</v>
+        <v>1180</v>
       </c>
       <c r="O114" s="9"/>
       <c r="P114" s="1" t="s">
-        <v>1078</v>
+        <v>1032</v>
       </c>
       <c r="Q114" s="1" t="s">
-        <v>1079</v>
+        <v>1033</v>
       </c>
       <c r="R114" s="1" t="s">
-        <v>1080</v>
+        <v>1034</v>
       </c>
       <c r="S114" s="1" t="s">
-        <v>1081</v>
+        <v>1035</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="U114" s="1" t="s">
         <v>29</v>
       </c>
       <c r="V114" s="1" t="s">
-        <v>1082</v>
+        <v>1036</v>
       </c>
       <c r="W114" s="1" t="s">
-        <v>1083</v>
+        <v>1037</v>
       </c>
       <c r="X114" s="1" t="s">
-        <v>1084</v>
+        <v>1038</v>
       </c>
       <c r="Y114" s="1" t="s">
-        <v>1085</v>
+        <v>1039</v>
       </c>
       <c r="Z114" s="1" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="AA114" s="1" t="s">
-        <v>1086</v>
+        <v>1040</v>
       </c>
       <c r="AB114" s="1" t="s">
-        <v>1087</v>
+        <v>1041</v>
       </c>
     </row>
-    <row r="115" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>1088</v>
+        <v>1042</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>1089</v>
+        <v>1043</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>1090</v>
+        <v>1044</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I115" s="8" t="s">
         <v>36</v>
@@ -12858,79 +12889,79 @@
         <v>36</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>1235</v>
+        <v>1181</v>
       </c>
       <c r="M115" s="1" t="s">
-        <v>1061</v>
+        <v>1015</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>1091</v>
+        <v>1045</v>
       </c>
       <c r="O115" s="9"/>
       <c r="P115" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q115" s="1" t="s">
-        <v>1092</v>
+        <v>1046</v>
       </c>
       <c r="R115" s="1" t="s">
-        <v>1093</v>
+        <v>1047</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>1094</v>
+        <v>1048</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>1095</v>
+        <v>1049</v>
       </c>
       <c r="U115" s="1" t="s">
-        <v>1096</v>
+        <v>1050</v>
       </c>
       <c r="V115" s="1" t="s">
-        <v>1097</v>
+        <v>1051</v>
       </c>
       <c r="W115" s="1" t="s">
-        <v>1098</v>
+        <v>1052</v>
       </c>
       <c r="X115" s="1" t="s">
-        <v>1099</v>
+        <v>1053</v>
       </c>
       <c r="Y115" s="1" t="s">
-        <v>1100</v>
+        <v>1054</v>
       </c>
       <c r="Z115" s="1" t="s">
-        <v>1101</v>
+        <v>1055</v>
       </c>
       <c r="AA115" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB115" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>1102</v>
+        <v>1056</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>1103</v>
+        <v>1057</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>1104</v>
+        <v>1058</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>1105</v>
+        <v>1059</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I116" s="8" t="s">
         <v>36</v>
@@ -12942,70 +12973,70 @@
         <v>36</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>1106</v>
+        <v>1060</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>1107</v>
+        <v>1061</v>
       </c>
       <c r="O116" s="9"/>
       <c r="P116" s="1" t="s">
-        <v>1108</v>
+        <v>1062</v>
       </c>
       <c r="Q116" s="1" t="s">
-        <v>1109</v>
+        <v>1063</v>
       </c>
       <c r="R116" s="1" t="s">
-        <v>1110</v>
+        <v>1064</v>
       </c>
       <c r="S116" s="1" t="s">
-        <v>1111</v>
+        <v>1065</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>1112</v>
+        <v>1066</v>
       </c>
       <c r="U116" s="1" t="s">
-        <v>1113</v>
+        <v>1067</v>
       </c>
       <c r="V116" s="1" t="s">
-        <v>1114</v>
+        <v>1068</v>
       </c>
       <c r="W116" s="1" t="s">
-        <v>1115</v>
+        <v>1069</v>
       </c>
       <c r="X116" s="1" t="s">
-        <v>1116</v>
+        <v>1070</v>
       </c>
       <c r="Y116" s="1" t="s">
-        <v>1117</v>
+        <v>1071</v>
       </c>
       <c r="Z116" s="1" t="s">
-        <v>1118</v>
+        <v>1072</v>
       </c>
       <c r="AA116" s="1" t="s">
-        <v>1119</v>
+        <v>1073</v>
       </c>
       <c r="AB116" s="1" t="s">
-        <v>1120</v>
+        <v>1074</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>1121</v>
+        <v>1075</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>1122</v>
+        <v>1076</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>1123</v>
+        <v>1077</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>1124</v>
+        <v>1078</v>
       </c>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
@@ -13019,23 +13050,23 @@
         <v>36</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>1106</v>
+        <v>1060</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>1125</v>
+        <v>1079</v>
       </c>
       <c r="O117" s="9"/>
       <c r="P117" s="1" t="s">
-        <v>1126</v>
+        <v>1080</v>
       </c>
       <c r="Q117" s="1" t="s">
-        <v>1127</v>
+        <v>1081</v>
       </c>
       <c r="R117" s="1" t="s">
-        <v>1128</v>
+        <v>1082</v>
       </c>
       <c r="S117" s="1" t="s">
-        <v>1126</v>
+        <v>1080</v>
       </c>
       <c r="T117" s="1" t="s">
         <v>29</v>
@@ -13044,45 +13075,45 @@
         <v>29</v>
       </c>
       <c r="V117" s="1" t="s">
-        <v>1129</v>
+        <v>1083</v>
       </c>
       <c r="W117" s="1" t="s">
-        <v>1115</v>
+        <v>1069</v>
       </c>
       <c r="X117" s="1" t="s">
-        <v>1130</v>
+        <v>1084</v>
       </c>
       <c r="Y117" s="1" t="s">
-        <v>1131</v>
+        <v>1085</v>
       </c>
       <c r="Z117" s="1" t="s">
         <v>29</v>
       </c>
       <c r="AA117" s="1" t="s">
-        <v>1132</v>
+        <v>1086</v>
       </c>
       <c r="AB117" s="1" t="s">
-        <v>1132</v>
+        <v>1086</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>1133</v>
+        <v>1087</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>1134</v>
+        <v>1088</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>1123</v>
+        <v>1077</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1135</v>
+        <v>1089</v>
       </c>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
@@ -13096,10 +13127,10 @@
         <v>36</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>1106</v>
+        <v>1060</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>1136</v>
+        <v>1090</v>
       </c>
       <c r="O118" s="9"/>
       <c r="P118" s="1" t="s">
@@ -13109,7 +13140,7 @@
         <v>29</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>1137</v>
+        <v>1091</v>
       </c>
       <c r="S118" s="1" t="s">
         <v>29</v>
@@ -13127,7 +13158,7 @@
         <v>29</v>
       </c>
       <c r="X118" s="1" t="s">
-        <v>1138</v>
+        <v>1092</v>
       </c>
       <c r="Y118" s="1" t="s">
         <v>29</v>
@@ -13136,21 +13167,21 @@
         <v>29</v>
       </c>
       <c r="AA118" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB118" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>1139</v>
+        <v>1093</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>1140</v>
+        <v>1094</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>32</v>
@@ -13159,13 +13190,13 @@
         <v>34</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>1141</v>
+        <v>1095</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="I119" s="8" t="s">
         <v>36</v>
@@ -13177,61 +13208,61 @@
         <v>36</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>1106</v>
+        <v>1060</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>1142</v>
+        <v>1096</v>
       </c>
       <c r="O119" s="9"/>
       <c r="P119" s="1" t="s">
-        <v>1143</v>
+        <v>1097</v>
       </c>
       <c r="Q119" s="1" t="s">
-        <v>1144</v>
+        <v>1098</v>
       </c>
       <c r="R119" s="1" t="s">
-        <v>1145</v>
+        <v>1099</v>
       </c>
       <c r="S119" s="1" t="s">
-        <v>1146</v>
+        <v>1100</v>
       </c>
       <c r="T119" s="1" t="s">
-        <v>1147</v>
+        <v>1101</v>
       </c>
       <c r="U119" s="1" t="s">
-        <v>1148</v>
+        <v>1102</v>
       </c>
       <c r="V119" s="1" t="s">
-        <v>1149</v>
+        <v>1103</v>
       </c>
       <c r="W119" s="1" t="s">
-        <v>1150</v>
+        <v>1104</v>
       </c>
       <c r="X119" s="1" t="s">
-        <v>1151</v>
+        <v>1105</v>
       </c>
       <c r="Y119" s="1" t="s">
-        <v>1152</v>
+        <v>1106</v>
       </c>
       <c r="Z119" s="1" t="s">
         <v>29</v>
       </c>
       <c r="AA119" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB119" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>1153</v>
+        <v>1107</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>1154</v>
+        <v>1108</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>32</v>
@@ -13240,13 +13271,13 @@
         <v>34</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1155</v>
+        <v>1109</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="I120" s="8" t="s">
         <v>36</v>
@@ -13258,10 +13289,10 @@
         <v>36</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>1106</v>
+        <v>1060</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>1156</v>
+        <v>1110</v>
       </c>
       <c r="O120" s="9"/>
       <c r="P120" s="1" t="s">
@@ -13283,7 +13314,7 @@
         <v>29</v>
       </c>
       <c r="V120" s="1" t="s">
-        <v>1157</v>
+        <v>1111</v>
       </c>
       <c r="W120" s="1" t="s">
         <v>29</v>
@@ -13298,21 +13329,21 @@
         <v>29</v>
       </c>
       <c r="AA120" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB120" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="180" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>1158</v>
+        <v>1112</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>1159</v>
+        <v>1113</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>32</v>
@@ -13321,13 +13352,13 @@
         <v>34</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>1160</v>
+        <v>1114</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="I121" s="8" t="s">
         <v>36</v>
@@ -13339,133 +13370,144 @@
         <v>36</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>1106</v>
+        <v>1060</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>1161</v>
+        <v>1115</v>
       </c>
       <c r="O121" s="9"/>
       <c r="P121" s="1" t="s">
-        <v>1162</v>
+        <v>1116</v>
       </c>
       <c r="Q121" s="1" t="s">
-        <v>1163</v>
+        <v>1117</v>
       </c>
       <c r="R121" s="1" t="s">
-        <v>1164</v>
+        <v>1118</v>
       </c>
       <c r="S121" s="1" t="s">
-        <v>1165</v>
+        <v>1119</v>
       </c>
       <c r="T121" s="1" t="s">
-        <v>1166</v>
+        <v>1120</v>
       </c>
       <c r="U121" s="1" t="s">
-        <v>1167</v>
+        <v>1121</v>
       </c>
       <c r="V121" s="1" t="s">
-        <v>1168</v>
+        <v>1122</v>
       </c>
       <c r="W121" s="1" t="s">
-        <v>1169</v>
+        <v>1123</v>
       </c>
       <c r="X121" s="1" t="s">
-        <v>1170</v>
+        <v>1124</v>
       </c>
       <c r="Y121" s="1" t="s">
-        <v>1171</v>
+        <v>1125</v>
       </c>
       <c r="Z121" s="1" t="s">
-        <v>1172</v>
+        <v>1126</v>
       </c>
       <c r="AA121" s="1" t="s">
-        <v>1173</v>
+        <v>1127</v>
       </c>
       <c r="AB121" s="1" t="s">
-        <v>1174</v>
+        <v>1128</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:28" ht="150" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>1175</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C123" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E123" s="1" t="s">
+    <row r="122" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="J123" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K123" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L123" s="1" t="s">
-        <v>1177</v>
-      </c>
-      <c r="M123" s="1" t="s">
-        <v>1178</v>
-      </c>
-      <c r="N123" s="1" t="s">
-        <v>1179</v>
-      </c>
-      <c r="O123" s="9"/>
-      <c r="P123" s="1" t="s">
-        <v>1180</v>
-      </c>
-      <c r="Q123" s="1" t="s">
-        <v>1181</v>
-      </c>
-      <c r="R123" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="S123" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="T123" s="1" t="s">
-        <v>1184</v>
-      </c>
-      <c r="U123" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="V123" s="1" t="s">
-        <v>1186</v>
-      </c>
-      <c r="W123" s="1" t="s">
-        <v>1187</v>
-      </c>
-      <c r="X123" s="1" t="s">
-        <v>1188</v>
-      </c>
-      <c r="Y123" s="1" t="s">
-        <v>1189</v>
-      </c>
-      <c r="Z123" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="AA123" s="1" t="s">
-        <v>1191</v>
-      </c>
-      <c r="AB123" s="1" t="s">
-        <v>1192</v>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J122" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K122" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="N122" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="O122" s="9"/>
+      <c r="P122" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="Q122" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="R122" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="S122" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="T122" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="U122" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="V122" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="W122" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="X122" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="Y122" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="Z122" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AA122" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AB122" s="1" t="s">
+        <v>1145</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N123" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:N122" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Analytical Mode"/>
+        <filter val="ICP-MS Manufacturer &amp; Model"/>
+        <filter val="Laser Manufacturer &amp; Model"/>
+        <filter val="Laser Spot Path / Ablation Mode"/>
+        <filter val="Plasma Thermal Mode"/>
+        <filter val="Signal Collection Mode"/>
+        <filter val="Triple Scanning Mode"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13500,27 +13542,27 @@
         <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1193</v>
+        <v>1146</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1194</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1195</v>
+        <v>1148</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1196</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -13528,29 +13570,29 @@
         <v>75</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1197</v>
+        <v>1150</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1198</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="C5" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1199</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>1200</v>
+        <v>1153</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1201</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -13576,7 +13618,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1202</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13584,7 +13626,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1203</v>
+        <v>1156</v>
       </c>
     </row>
   </sheetData>

--- a/docs/LA-Q_SF-ICPMS_TAPP_v3.xlsx
+++ b/docs/LA-Q_SF-ICPMS_TAPP_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithubC\USGIN\geochemBuildingBlocks\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AA343C-5525-42D1-84DE-533E6CF993C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE9A940-7394-4748-A172-D28D13036DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1215" windowWidth="26520" windowHeight="14805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-585" yWindow="4035" windowWidth="28350" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAPP" sheetId="1" r:id="rId1"/>
@@ -3971,9 +3971,6 @@
     <t>$MethodDefinition.ada:massResolutionPerAnalyte[]</t>
   </si>
   <si>
-    <t>$MethodDefinition.ada:backgroundCountTime[]</t>
-  </si>
-  <si>
     <t>$MethodDefinition.ada:elementalFractionationCorrection[]</t>
   </si>
   <si>
@@ -4156,6 +4153,9 @@
   </si>
   <si>
     <t>$MethodDefinition.schema:additionalProperty[schema:name = 'Doubly-Charged Species Production'].schema:defaultValue</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.ada:backgroundCountTime</t>
   </si>
 </sst>
 </file>
@@ -4642,7 +4642,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AB122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4753,7 +4752,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
@@ -4786,7 +4785,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
@@ -4863,7 +4862,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>50</v>
       </c>
@@ -4940,7 +4939,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
@@ -5020,7 +5019,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>73</v>
       </c>
@@ -5051,10 +5050,10 @@
         <v>36</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="O6" s="9"/>
       <c r="P6" s="1" t="s">
@@ -5097,7 +5096,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>79</v>
       </c>
@@ -5128,7 +5127,7 @@
         <v>36</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>83</v>
@@ -5174,7 +5173,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>92</v>
       </c>
@@ -5254,7 +5253,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>100</v>
       </c>
@@ -5334,7 +5333,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>107</v>
       </c>
@@ -5411,7 +5410,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>111</v>
       </c>
@@ -5485,7 +5484,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>114</v>
       </c>
@@ -5516,10 +5515,10 @@
         <v>36</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>118</v>
@@ -5565,7 +5564,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>119</v>
       </c>
@@ -5647,7 +5646,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>132</v>
       </c>
@@ -5680,7 +5679,7 @@
         <v>36</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="O14" s="9"/>
       <c r="P14" s="1" t="s">
@@ -5723,7 +5722,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>144</v>
       </c>
@@ -5754,7 +5753,7 @@
         <v>36</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>147</v>
@@ -5803,7 +5802,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>158</v>
       </c>
@@ -5836,7 +5835,7 @@
         <v>36</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>162</v>
@@ -5885,7 +5884,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>167</v>
       </c>
@@ -5918,7 +5917,7 @@
         <v>36</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>170</v>
@@ -5967,7 +5966,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>176</v>
       </c>
@@ -6000,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="O18" s="9"/>
       <c r="P18" s="1" t="s">
@@ -6043,7 +6042,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="255" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>180</v>
       </c>
@@ -6076,7 +6075,7 @@
         <v>36</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="O19" s="9"/>
       <c r="P19" s="1" t="s">
@@ -6119,8 +6118,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="8.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>184</v>
       </c>
@@ -6153,7 +6152,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>185</v>
       </c>
@@ -6184,10 +6183,10 @@
         <v>36</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>188</v>
@@ -6233,7 +6232,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>200</v>
       </c>
@@ -6264,7 +6263,7 @@
         <v>36</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>203</v>
@@ -6313,7 +6312,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>218</v>
       </c>
@@ -6387,7 +6386,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>223</v>
       </c>
@@ -6461,7 +6460,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>228</v>
       </c>
@@ -6492,7 +6491,7 @@
         <v>36</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>231</v>
@@ -6541,7 +6540,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="180" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>235</v>
       </c>
@@ -6621,7 +6620,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>254</v>
       </c>
@@ -6652,7 +6651,7 @@
         <v>36</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>257</v>
@@ -6701,8 +6700,8 @@
         <v>262</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="8.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>263</v>
       </c>
@@ -6768,10 +6767,10 @@
         <v>36</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>38</v>
@@ -6848,10 +6847,10 @@
         <v>36</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>38</v>
@@ -6897,7 +6896,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>285</v>
       </c>
@@ -6930,7 +6929,7 @@
         <v>36</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>1157</v>
@@ -6979,7 +6978,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>299</v>
       </c>
@@ -7012,7 +7011,7 @@
         <v>36</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="O34" s="9"/>
       <c r="P34" s="1" t="s">
@@ -7055,7 +7054,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>303</v>
       </c>
@@ -7088,7 +7087,7 @@
         <v>36</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>1157</v>
@@ -7137,7 +7136,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>311</v>
       </c>
@@ -7170,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>315</v>
@@ -7190,7 +7189,7 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
     </row>
-    <row r="37" spans="1:28" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="180" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>316</v>
       </c>
@@ -7223,7 +7222,7 @@
         <v>36</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>319</v>
@@ -7243,7 +7242,7 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
     </row>
-    <row r="38" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>320</v>
       </c>
@@ -7276,7 +7275,7 @@
         <v>36</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="O38" s="9"/>
       <c r="P38" s="1" t="s">
@@ -7319,7 +7318,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>323</v>
       </c>
@@ -7350,7 +7349,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>326</v>
@@ -7396,7 +7395,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" ht="135" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>328</v>
       </c>
@@ -7431,7 +7430,7 @@
         <v>36</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>332</v>
@@ -7477,7 +7476,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>341</v>
       </c>
@@ -7508,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>344</v>
@@ -7554,7 +7553,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="345" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>351</v>
       </c>
@@ -7589,7 +7588,7 @@
         <v>36</v>
       </c>
       <c r="L42" s="21" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>344</v>
@@ -7635,7 +7634,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>355</v>
       </c>
@@ -7668,7 +7667,7 @@
         <v>36</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>358</v>
@@ -7714,7 +7713,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>366</v>
       </c>
@@ -7794,7 +7793,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>372</v>
       </c>
@@ -7876,7 +7875,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>387</v>
       </c>
@@ -7909,7 +7908,7 @@
         <v>36</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>358</v>
@@ -7955,8 +7954,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="8.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:28" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>395</v>
       </c>
@@ -8047,7 +8046,7 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
     </row>
-    <row r="50" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" ht="135" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>404</v>
       </c>
@@ -8080,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="N50" s="1" t="s">
         <v>407</v>
@@ -8159,7 +8158,7 @@
         <v>36</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="N51" s="1" t="s">
         <v>424</v>
@@ -8205,7 +8204,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>433</v>
       </c>
@@ -8236,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>437</v>
@@ -8282,7 +8281,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="53" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>439</v>
       </c>
@@ -8315,7 +8314,7 @@
         <v>36</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>444</v>
@@ -8361,7 +8360,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>456</v>
       </c>
@@ -8394,7 +8393,7 @@
         <v>36</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>460</v>
@@ -8440,7 +8439,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>461</v>
       </c>
@@ -8473,7 +8472,7 @@
         <v>36</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>465</v>
@@ -8519,7 +8518,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>473</v>
       </c>
@@ -8552,7 +8551,7 @@
         <v>36</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="N56" s="1" t="s">
         <v>460</v>
@@ -8598,7 +8597,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" ht="255" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>484</v>
       </c>
@@ -8678,7 +8677,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>499</v>
       </c>
@@ -8709,7 +8708,7 @@
         <v>36</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="N58" s="1" t="s">
         <v>502</v>
@@ -8755,7 +8754,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>509</v>
       </c>
@@ -8835,7 +8834,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>519</v>
       </c>
@@ -8914,7 +8913,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" ht="135" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>532</v>
       </c>
@@ -8947,7 +8946,7 @@
         <v>36</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>535</v>
@@ -8993,7 +8992,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>545</v>
       </c>
@@ -9072,7 +9071,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" ht="135" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>556</v>
       </c>
@@ -9151,7 +9150,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" ht="135" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>559</v>
       </c>
@@ -9312,7 +9311,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>581</v>
       </c>
@@ -9345,7 +9344,7 @@
         <v>36</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>584</v>
@@ -9391,7 +9390,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="67" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>588</v>
       </c>
@@ -9424,7 +9423,7 @@
         <v>36</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>591</v>
@@ -9470,7 +9469,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="68" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>599</v>
       </c>
@@ -9547,7 +9546,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="69" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>611</v>
       </c>
@@ -9578,7 +9577,7 @@
         <v>36</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="N69" s="1" t="s">
         <v>614</v>
@@ -9624,7 +9623,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="70" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>616</v>
       </c>
@@ -9657,7 +9656,7 @@
         <v>36</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="N70" s="1" t="s">
         <v>619</v>
@@ -9677,7 +9676,7 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
     </row>
-    <row r="71" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>620</v>
       </c>
@@ -9710,7 +9709,7 @@
         <v>36</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="N71" s="1" t="s">
         <v>623</v>
@@ -9730,7 +9729,7 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
     </row>
-    <row r="72" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>624</v>
       </c>
@@ -9807,7 +9806,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="73" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>629</v>
       </c>
@@ -9884,7 +9883,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="74" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>646</v>
       </c>
@@ -9966,7 +9965,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="75" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>665</v>
       </c>
@@ -10047,7 +10046,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="76" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>668</v>
       </c>
@@ -10128,7 +10127,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" ht="135" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>670</v>
       </c>
@@ -10163,7 +10162,7 @@
         <v>36</v>
       </c>
       <c r="L77" s="21" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="O77" s="9"/>
       <c r="P77" s="1" t="s">
@@ -10241,7 +10240,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="21" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="O78" s="9"/>
       <c r="P78" s="1" t="s">
@@ -10319,7 +10318,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="21" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="N79" s="1" t="s">
         <v>1165</v>
@@ -10365,7 +10364,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="80" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>681</v>
       </c>
@@ -10400,7 +10399,7 @@
         <v>36</v>
       </c>
       <c r="L80" s="21" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>1176</v>
@@ -10446,7 +10445,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="81" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>683</v>
       </c>
@@ -10481,7 +10480,7 @@
         <v>36</v>
       </c>
       <c r="L81" s="21" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="N81" s="1" t="s">
         <v>1170</v>
@@ -10527,7 +10526,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="82" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>686</v>
       </c>
@@ -10562,7 +10561,7 @@
         <v>36</v>
       </c>
       <c r="L82" s="21" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="N82" s="1" t="s">
         <v>1169</v>
@@ -10608,7 +10607,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="83" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>689</v>
       </c>
@@ -10643,7 +10642,7 @@
         <v>36</v>
       </c>
       <c r="L83" s="21" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="O83" s="9"/>
       <c r="P83" s="1" t="s">
@@ -10686,7 +10685,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="84" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>692</v>
       </c>
@@ -10721,7 +10720,7 @@
         <v>36</v>
       </c>
       <c r="L84" s="21" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="O84" s="9"/>
       <c r="P84" s="1" t="s">
@@ -10764,7 +10763,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:28" ht="189" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" ht="189" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>695</v>
       </c>
@@ -10845,7 +10844,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="86" spans="1:28" ht="200.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" ht="200.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>706</v>
       </c>
@@ -10876,7 +10875,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="N86" s="1" t="s">
         <v>1166</v>
@@ -10922,7 +10921,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="87" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>720</v>
       </c>
@@ -10999,7 +10998,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="88" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>736</v>
       </c>
@@ -11030,7 +11029,7 @@
         <v>36</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>739</v>
@@ -11079,7 +11078,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="89" spans="1:28" ht="66" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>741</v>
       </c>
@@ -11110,7 +11109,7 @@
         <v>36</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="N89" s="1" t="s">
         <v>745</v>
@@ -11156,7 +11155,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="90" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>758</v>
       </c>
@@ -11233,7 +11232,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="91" spans="1:28" ht="76.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>765</v>
       </c>
@@ -11310,8 +11309,8 @@
         <v>508</v>
       </c>
     </row>
-    <row r="92" spans="1:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:28" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:28" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
         <v>774</v>
       </c>
@@ -11344,7 +11343,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="94" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>775</v>
       </c>
@@ -11423,7 +11422,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="95" spans="1:28" ht="123.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>793</v>
       </c>
@@ -11502,7 +11501,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="96" spans="1:28" ht="279" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" ht="279" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>811</v>
       </c>
@@ -11560,7 +11559,7 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
     </row>
-    <row r="97" spans="1:28" ht="159.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:28" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>816</v>
       </c>
@@ -11591,7 +11590,7 @@
         <v>36</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="N97" s="1" t="s">
         <v>819</v>
@@ -11637,7 +11636,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="98" spans="1:28" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:28" ht="240" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>833</v>
       </c>
@@ -11668,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="N98" s="1" t="s">
         <v>836</v>
@@ -11714,7 +11713,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="99" spans="1:28" ht="2.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:28" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>844</v>
       </c>
@@ -11791,7 +11790,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="100" spans="1:28" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>856</v>
       </c>
@@ -11868,7 +11867,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="101" spans="1:28" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:28" ht="270" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>874</v>
       </c>
@@ -11945,7 +11944,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="102" spans="1:28" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:28" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>886</v>
       </c>
@@ -12022,7 +12021,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="103" spans="1:28" ht="180" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:28" ht="180" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>903</v>
       </c>
@@ -12099,7 +12098,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="104" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>921</v>
       </c>
@@ -12178,7 +12177,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="105" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:28" ht="135" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>934</v>
       </c>
@@ -12262,7 +12261,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="106" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:28" ht="135" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>950</v>
       </c>
@@ -12346,7 +12345,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="107" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>964</v>
       </c>
@@ -12430,7 +12429,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="108" spans="1:28" ht="99.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>978</v>
       </c>
@@ -12509,7 +12508,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="109" spans="1:28" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:28" ht="210" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>981</v>
       </c>
@@ -12586,7 +12585,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="110" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:28" ht="135" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>994</v>
       </c>
@@ -12617,7 +12616,7 @@
         <v>36</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="N110" s="1" t="s">
         <v>997</v>
@@ -12663,8 +12662,8 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="111" spans="1:28" ht="8.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:28" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:28" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>1011</v>
       </c>
@@ -12697,7 +12696,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>1012</v>
       </c>
@@ -12728,7 +12727,7 @@
         <v>36</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>1015</v>
@@ -12777,7 +12776,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="114" spans="1:28" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>1029</v>
       </c>
@@ -12810,7 +12809,7 @@
         <v>36</v>
       </c>
       <c r="L114" s="21" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="N114" s="1" t="s">
         <v>1180</v>
@@ -12856,7 +12855,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="115" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>1042</v>
       </c>
@@ -12938,7 +12937,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>1056</v>
       </c>
@@ -13019,7 +13018,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>1075</v>
       </c>
@@ -13096,7 +13095,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>1087</v>
       </c>
@@ -13173,7 +13172,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" ht="225" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>1093</v>
       </c>
@@ -13254,7 +13253,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>1107</v>
       </c>
@@ -13335,7 +13334,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" ht="180" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>1112</v>
       </c>
@@ -13416,7 +13415,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>1129</v>
       </c>
@@ -13445,7 +13444,7 @@
         <v>36</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="M122" s="1" t="s">
         <v>1131</v>
@@ -13495,19 +13494,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N122" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Analytical Mode"/>
-        <filter val="ICP-MS Manufacturer &amp; Model"/>
-        <filter val="Laser Manufacturer &amp; Model"/>
-        <filter val="Laser Spot Path / Ablation Mode"/>
-        <filter val="Plasma Thermal Mode"/>
-        <filter val="Signal Collection Mode"/>
-        <filter val="Triple Scanning Mode"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N122" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
